--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>骨子案 第1章4（基本指針改正16項目、法定雇用率2.7%）／年齢到達による給付移行 調査報告</t>
+          <t>骨子案 第1章4（基本指針改正16項目、法定雇用率2.7%）／年齢到達による給付移行 調査報告／現行計画本編 第4章1（第7期の基本指針見直し）</t>
         </is>
       </c>
       <c r="E17" s="33" t="inlineStr">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="F17" s="9" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G17" s="32" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>前回計画評価_アンケート精査管理表（01_前回計画評価／06_R6-R8実績入力様式）／前回計画課題整理メモ</t>
+          <t>前回計画評価_アンケート精査管理表／前回計画課題整理メモ／現行計画本編（受領済）</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>令和6・7年度実績と令和8年度見込を受領するまで達成判定が確定できない</t>
+          <t>現行計画本編の受領により目標値・設定根拠・令和3〜5年度実績が確定。令和6・7年度実績と令和8年度見込を受領するまで達成判定は確定できない</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="G19" s="32" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>令和6〜8年度実績と年齢階級別内訳を受領し、方法C（年齢階級別所持率法）へ切り替える</t>
+          <t>現行計画本編の受領により年齢3区分別人口5年分が判明し、所持率の推移を算定できた。令和6〜8年度実績と年齢階級別内訳を受領し、方法C（年齢階級別所持率法）へ切り替える</t>
         </is>
       </c>
     </row>
@@ -4116,34 +4116,34 @@
       <c r="G13" s="37" t="n"/>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>前回調査の原本・単純集計・自由記述分類</t>
+          <t>前回調査の調査結果報告書</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>回収率57.9%の内訳を含む</t>
+          <t>発送164人・回収95人・回収率57.9%。設問別の集計結果を収録</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>アンケート集計設計</t>
-        </is>
-      </c>
-      <c r="E14" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+          <t>アンケート集計設計・経年比較</t>
+        </is>
+      </c>
+      <c r="E14" s="36" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G14" s="37" t="n"/>
@@ -4250,7 +4250,7 @@
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -4260,22 +4260,22 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>原本が未受領のため、前回計画の推計方法は二次資料からの復元にとどまっている</t>
+          <t>本編63頁、アンケート調査結果報告書69頁、概要版4頁。令和6年3月策定</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>全体</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+          <t>全体（年齢3区分別人口・前回調査の内訳を反映済み）</t>
+        </is>
+      </c>
+      <c r="E18" s="36" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G18" s="37" t="n"/>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>仕様書の約190人と現行計画の156人に22%の差。実数であれば手帳推計の方向が逆になる</t>
+          <t>仕様書の約190人と現行計画の156人に22%の差。実数であれば手帳推計の方向が逆になる。前回調査は手帳所持者156人＋サービス利用者8人＝164人（重複3人含む）を発送しており、所持率トレンドを延長しても令和8年は157人にとどまる</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -5058,7 +5058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5111,17 +5111,17 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>進捗管理</t>
+          <t>資料受領</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>業務進捗管理ブックを新規作成。仕様書条項別の進捗台帳、村資料受領状況、課題・リスクを一本化</t>
+          <t>現行計画本編・アンケート調査結果報告書・概要版を受領。年齢3区分別人口5年分、前回調査の内訳（発送164人・回収95人）、成果目標の設定根拠が確定。将来推計・給付費の記載がないことを一次確認</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_業務進捗管理.xlsx</t>
+          <t>現行計画本編（3379.pdf）／調査結果報告書（3380.pdf）／概要版（3388.pdf）</t>
         </is>
       </c>
     </row>
@@ -5133,17 +5133,17 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>推計方法</t>
+          <t>進捗管理</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量を個別積上げ方式へ切替。計画素案に第5章1（見込量の推計方法）・第5章2（年齢到達に伴うサービスの移行）を新設</t>
+          <t>業務進捗管理ブックを新規作成。仕様書条項別の進捗台帳、村資料受領状況、課題・リスクを一本化</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_サービス見込量.xlsx／北塩原村_骨子案_修正版.docx</t>
+          <t>北塩原村_業務進捗管理.xlsx</t>
         </is>
       </c>
     </row>
@@ -5155,17 +5155,17 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>調査</t>
+          <t>推計方法</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>年齢到達による給付の終了・移行を調査。骨子案に65歳・18歳の記述が0件、障がい者票に介護保険の設問がないことを確認</t>
+          <t>サービス見込量を個別積上げ方式へ切替。計画素案に第5章1（見込量の推計方法）・第5章2（年齢到達に伴うサービスの移行）を新設</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_年齢到達による給付移行_調査報告.md</t>
+          <t>北塩原村_サービス見込量.xlsx／北塩原村_骨子案_修正版.docx</t>
         </is>
       </c>
     </row>
@@ -5177,17 +5177,17 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>検証</t>
+          <t>調査</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>推計方法のレッドチーム検証。時点表記の1年ずれ、方法Aの予測区間、方法Bの分母感度、過去稿の記載と計算の不一致を検出・修正</t>
+          <t>年齢到達による給付の終了・移行を調査。骨子案に65歳・18歳の記述が0件、障がい者票に介護保険の設問がないことを確認</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_推計方法_レッドチーム検証.md</t>
+          <t>北塩原村_年齢到達による給付移行_調査報告.md</t>
         </is>
       </c>
     </row>
@@ -5199,17 +5199,17 @@
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>計画素案</t>
+          <t>検証</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>骨子案を正本とし、手帳将来推計・最新人口・財源構成・こども家庭センターを移植</t>
+          <t>推計方法のレッドチーム検証。時点表記の1年ずれ、方法Aの予測区間、方法Bの分母感度、過去稿の記載と計算の不一致を検出・修正</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_骨子案_修正版.docx</t>
+          <t>北塩原村_推計方法_レッドチーム検証.md</t>
         </is>
       </c>
     </row>
@@ -5221,17 +5221,17 @@
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>レビュー</t>
+          <t>計画素案</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>骨子案★版と計画素案第9稿を比較し、正本を骨子案に決定</t>
+          <t>骨子案を正本とし、手帳将来推計・最新人口・財源構成・こども家庭センターを移植</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_骨子案_計画素案第9稿_比較レビュー.md</t>
+          <t>北塩原村_骨子案_修正版.docx</t>
         </is>
       </c>
     </row>
@@ -5243,91 +5243,107 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>受注整理</t>
+          <t>レビュー</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>仕様書・議事録・成果物を突合し受注内容を整理</t>
+          <t>骨子案★版と計画素案第9稿を比較し、正本を骨子案に決定</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_第8期障がい福祉計画_受注内容整理.md</t>
+          <t>北塩原村_骨子案_計画素案第9稿_比較レビュー.md</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
-          <t>調査票</t>
+          <t>受注整理</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>0728版アンケート調査票のレビュー（障がい者52問・障がい児51問）</t>
+          <t>仕様書・議事録・成果物を突合し受注内容を整理</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>0728北塩原村_障がい福祉／障がい児福祉アンケート調査票.docx</t>
+          <t>北塩原村_第8期障がい福祉計画_受注内容整理.md</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>障がいサービス給付実績（令和2〜7年度）を整理</t>
+          <t>0728版アンケート調査票のレビュー（障がい者52問・障がい児51問）</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_障がいサービス給付実績_整理版.xlsx</t>
+          <t>0728北塩原村_障がい福祉／障がい児福祉アンケート調査票.docx</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>障がいサービス給付実績（令和2〜7年度）を整理</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>北塩原村_障がいサービス給付実績_整理版.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>打合せ</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>北塩原村役場にて打合せ。アンケート実施設計を決定</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>議事録</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="37" t="n"/>
-      <c r="B16" s="38" t="n"/>
-      <c r="C16" s="39" t="n"/>
-      <c r="D16" s="39" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
@@ -5358,6 +5374,12 @@
       <c r="B21" s="38" t="n"/>
       <c r="C21" s="39" t="n"/>
       <c r="D21" s="39" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="37" t="n"/>
+      <c r="B22" s="38" t="n"/>
+      <c r="C22" s="39" t="n"/>
+      <c r="D22" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_仕様書別進捗'!$A$5:$I$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1971,16 +1971,16 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>前回計画評価_アンケート精査管理表／前回計画課題整理メモ／現行計画本編（受領済）</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t>村資料待ち</t>
+          <t>北塩原村_現行計画評価.xlsx（7シート）／前回計画評価_アンケート精査管理表／現行計画本編</t>
+        </is>
+      </c>
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>作業中</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>現行計画本編の受領により目標値・設定根拠・令和3〜5年度実績が確定。令和6・7年度実績と令和8年度見込を受領するまで達成判定は確定できない</t>
+          <t>令和3〜5年度の見込量と実績の突合（サービス25区分・地域生活支援事業13事業）を完了。令和6・7年度実績と令和8年度見込を受領するまで第7期の達成判定は確定できない</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>骨子案 第3章／計画素案 第9稿 第6章（9分野）</t>
+          <t>北塩原村_現行計画評価.xlsx（03_施策目標と測定手段・06_次期計画への引継ぎ）／骨子案 第3章</t>
         </is>
       </c>
       <c r="E24" s="34" t="inlineStr">
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G24" s="30" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>施策体系を本計画の内容として位置づけるか、第4次障がい者計画の参考として扱うかの方針決定</t>
+          <t>第4次障がい者計画の施策目標8指標の測定手段を確認済み。施策体系を本計画の内容として位置づけるか、参考として扱うかの方針決定が残る</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3245,17 +3245,17 @@
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>管理</t>
+          <t>評価</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_業務進捗管理.xlsx</t>
+          <t>北塩原村_現行計画評価.xlsx</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>本ブック</t>
+          <t>現行計画の評価（7シート）</t>
         </is>
       </c>
       <c r="D16" s="24" t="n"/>
@@ -3267,36 +3267,36 @@
       <c r="F16" s="24" t="n"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>納品対象とするか村と確認</t>
+          <t>令和3〜5年度の見込量と実績の突合、成果目標・施策目標の評価</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="32" t="inlineStr">
         <is>
-          <t>調査</t>
+          <t>管理</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>0728北塩原村_障がい福祉アンケート調査票.docx</t>
+          <t>北塩原村_業務進捗管理.xlsx</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>調査票（障がい者版・52問）</t>
+          <t>本ブック</t>
         </is>
       </c>
       <c r="D17" s="24" t="n"/>
-      <c r="E17" s="33" t="inlineStr">
-        <is>
-          <t>概ね完了</t>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>作業中</t>
         </is>
       </c>
       <c r="F17" s="24" t="n"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>最終目視確認が残</t>
+          <t>納品対象とするか村と確認</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>0728北塩原村_障がい児福祉アンケート調査票.docx</t>
+          <t>0728北塩原村_障がい福祉アンケート調査票.docx</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>調査票（障がい児版・51問）</t>
+          <t>調査票（障がい者版・52問）</t>
         </is>
       </c>
       <c r="D18" s="24" t="n"/>
@@ -3325,7 +3325,7 @@
       <c r="F18" s="24" t="n"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>ルビ構造の確認が残</t>
+          <t>最終目視確認が残</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Googleフォーム自動作成 Code（.gs）</t>
+          <t>0728北塩原村_障がい児福祉アンケート調査票.docx</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>ウェブ回答フォームの生成スクリプト</t>
+          <t>調査票（障がい児版・51問）</t>
         </is>
       </c>
       <c r="D19" s="24" t="n"/>
@@ -3354,70 +3354,99 @@
       <c r="F19" s="24" t="n"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>選択肢順序の固定が残</t>
+          <t>ルビ構造の確認が残</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>調査</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_障がいサービス給付実績_整理版.xlsx</t>
+          <t>Googleフォーム自動作成 Code（.gs）</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>受領データの整理版（6シート）</t>
+          <t>ウェブ回答フォームの生成スクリプト</t>
         </is>
       </c>
       <c r="D20" s="24" t="n"/>
-      <c r="E20" s="36" t="inlineStr">
-        <is>
-          <t>完了</t>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>概ね完了</t>
         </is>
       </c>
       <c r="F20" s="24" t="n"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>令和2〜7年度、介護給付費・障害児給付費</t>
+          <t>選択肢順序の固定が残</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t>報告</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>調査結果報告書（未作成）</t>
+          <t>北塩原村_障がいサービス給付実績_整理版.xlsx</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>アンケート集計結果</t>
+          <t>受領データの整理版（6シート）</t>
         </is>
       </c>
       <c r="D21" s="24" t="n"/>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="E21" s="36" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="F21" s="24" t="n"/>
       <c r="G21" s="7" t="inlineStr">
         <is>
+          <t>令和2〜7年度、介護給付費・障害児給付費</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>報告</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>調査結果報告書（未作成）</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>アンケート集計結果</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
           <t>集計後</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="25">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C14:D14"/>
@@ -3429,6 +3458,7 @@
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C21:D21"/>
@@ -3437,6 +3467,7 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:F18"/>
@@ -4469,7 +4500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4868,42 +4899,79 @@
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="32" t="inlineStr">
         <is>
+          <t>R-11</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>第4次障がい者計画の施策目標のうち1指標が測定できない</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>発送前であれば問13の後に外出目的の設問を追加するか、問45の選択肢を前回に揃える。発送後であれば別の把握方法へ切り替える旨を村と協議する</t>
+        </is>
+      </c>
+      <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>判断待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>供給</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>圏域事業所の受入可能量が見込量の上限になる</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>村内に事業所がなく、送迎・人材・定員が制約となる</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>圏域事業所へ照会し、利用希望量と利用可能量を分けて管理する</t>
         </is>
       </c>
-      <c r="G15" s="32" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G15"/>
+  <autoFilter ref="A5:G16"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -5058,7 +5126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5111,17 +5179,17 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>資料受領</t>
+          <t>評価</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>現行計画本編・アンケート調査結果報告書・概要版を受領。年齢3区分別人口5年分、前回調査の内訳（発送164人・回収95人）、成果目標の設定根拠が確定。将来推計・給付費の記載がないことを一次確認</t>
+          <t>現行計画評価ブックを作成。令和3〜5年度の見込量と実績を突合し、計上漏れ2件・過大計上3件・施策指標1件の測定不能を検出</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>現行計画本編（3379.pdf）／調査結果報告書（3380.pdf）／概要版（3388.pdf）</t>
+          <t>北塩原村_現行計画評価.xlsx</t>
         </is>
       </c>
     </row>
@@ -5133,17 +5201,17 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>進捗管理</t>
+          <t>資料受領</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>業務進捗管理ブックを新規作成。仕様書条項別の進捗台帳、村資料受領状況、課題・リスクを一本化</t>
+          <t>現行計画本編・アンケート調査結果報告書・概要版を受領。年齢3区分別人口5年分、前回調査の内訳（発送164人・回収95人）、成果目標の設定根拠が確定。将来推計・給付費の記載がないことを一次確認</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_業務進捗管理.xlsx</t>
+          <t>現行計画本編（3379.pdf）／調査結果報告書（3380.pdf）／概要版（3388.pdf）</t>
         </is>
       </c>
     </row>
@@ -5155,17 +5223,17 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>推計方法</t>
+          <t>進捗管理</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>サービス見込量を個別積上げ方式へ切替。計画素案に第5章1（見込量の推計方法）・第5章2（年齢到達に伴うサービスの移行）を新設</t>
+          <t>業務進捗管理ブックを新規作成。仕様書条項別の進捗台帳、村資料受領状況、課題・リスクを一本化</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_サービス見込量.xlsx／北塩原村_骨子案_修正版.docx</t>
+          <t>北塩原村_業務進捗管理.xlsx</t>
         </is>
       </c>
     </row>
@@ -5177,17 +5245,17 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>調査</t>
+          <t>推計方法</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>年齢到達による給付の終了・移行を調査。骨子案に65歳・18歳の記述が0件、障がい者票に介護保険の設問がないことを確認</t>
+          <t>サービス見込量を個別積上げ方式へ切替。計画素案に第5章1（見込量の推計方法）・第5章2（年齢到達に伴うサービスの移行）を新設</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_年齢到達による給付移行_調査報告.md</t>
+          <t>北塩原村_サービス見込量.xlsx／北塩原村_骨子案_修正版.docx</t>
         </is>
       </c>
     </row>
@@ -5199,17 +5267,17 @@
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>検証</t>
+          <t>調査</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>推計方法のレッドチーム検証。時点表記の1年ずれ、方法Aの予測区間、方法Bの分母感度、過去稿の記載と計算の不一致を検出・修正</t>
+          <t>年齢到達による給付の終了・移行を調査。骨子案に65歳・18歳の記述が0件、障がい者票に介護保険の設問がないことを確認</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_推計方法_レッドチーム検証.md</t>
+          <t>北塩原村_年齢到達による給付移行_調査報告.md</t>
         </is>
       </c>
     </row>
@@ -5221,17 +5289,17 @@
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>計画素案</t>
+          <t>検証</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>骨子案を正本とし、手帳将来推計・最新人口・財源構成・こども家庭センターを移植</t>
+          <t>推計方法のレッドチーム検証。時点表記の1年ずれ、方法Aの予測区間、方法Bの分母感度、過去稿の記載と計算の不一致を検出・修正</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_骨子案_修正版.docx</t>
+          <t>北塩原村_推計方法_レッドチーム検証.md</t>
         </is>
       </c>
     </row>
@@ -5243,17 +5311,17 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>レビュー</t>
+          <t>計画素案</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>骨子案★版と計画素案第9稿を比較し、正本を骨子案に決定</t>
+          <t>骨子案を正本とし、手帳将来推計・最新人口・財源構成・こども家庭センターを移植</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_骨子案_計画素案第9稿_比較レビュー.md</t>
+          <t>北塩原村_骨子案_修正版.docx</t>
         </is>
       </c>
     </row>
@@ -5265,91 +5333,107 @@
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
-          <t>受注整理</t>
+          <t>レビュー</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>仕様書・議事録・成果物を突合し受注内容を整理</t>
+          <t>骨子案★版と計画素案第9稿を比較し、正本を骨子案に決定</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_第8期障がい福祉計画_受注内容整理.md</t>
+          <t>北塩原村_骨子案_計画素案第9稿_比較レビュー.md</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>調査票</t>
+          <t>受注整理</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>0728版アンケート調査票のレビュー（障がい者52問・障がい児51問）</t>
+          <t>仕様書・議事録・成果物を突合し受注内容を整理</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>0728北塩原村_障がい福祉／障がい児福祉アンケート調査票.docx</t>
+          <t>北塩原村_第8期障がい福祉計画_受注内容整理.md</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>障がいサービス給付実績（令和2〜7年度）を整理</t>
+          <t>0728版アンケート調査票のレビュー（障がい者52問・障がい児51問）</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_障がいサービス給付実績_整理版.xlsx</t>
+          <t>0728北塩原村_障がい福祉／障がい児福祉アンケート調査票.docx</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="22" t="inlineStr">
         <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>障がいサービス給付実績（令和2〜7年度）を整理</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>北塩原村_障がいサービス給付実績_整理版.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>打合せ</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>北塩原村役場にて打合せ。アンケート実施設計を決定</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>議事録</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="37" t="n"/>
-      <c r="B17" s="38" t="n"/>
-      <c r="C17" s="39" t="n"/>
-      <c r="D17" s="39" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
@@ -5380,6 +5464,12 @@
       <c r="B22" s="38" t="n"/>
       <c r="C22" s="39" t="n"/>
       <c r="D22" s="39" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="37" t="n"/>
+      <c r="B23" s="38" t="n"/>
+      <c r="C23" s="39" t="n"/>
+      <c r="D23" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -2241,16 +2241,16 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_現行計画評価.xlsx（03_施策目標と測定手段・06_次期計画への引継ぎ）／骨子案 第3章</t>
-        </is>
-      </c>
-      <c r="E24" s="34" t="inlineStr">
-        <is>
-          <t>作業中</t>
+          <t>骨子案修正版 第3章（再構成済み）／北塩原村_現行計画評価.xlsx（03・06）</t>
+        </is>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>概ね完了</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="G24" s="30" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の施策目標8指標の測定手段を確認済み。施策体系を本計画の内容として位置づけるか、参考として扱うかの方針決定が残る</t>
+          <t>第3章を「計画の基本理念・基本目標及び施策体系」へ再構成し、第8期で加わる視点と施策体系の対応表を新設。中間年評価の実績値の反映が残る</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>骨子案修正版（全8章＋新設5節）</t>
+          <t>骨子案修正版（全8章。第2章6・第3章・第5章1・2・11を新設又は再構成）</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="G25" s="32" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>①基本理念・基本目標と②施策体系が「参考」扱いのため、本計画の内容として位置づける</t>
+          <t>8事項のうち①基本理念・基本目標と②施策体系を第3章で措置済み。③〜⑦は村資料の受領後に数値を確定する。⑧推進体制は第1章6</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5179,17 +5179,17 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>評価</t>
+          <t>計画素案</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>現行計画評価ブックを作成。令和3〜5年度の見込量と実績を突合し、計上漏れ2件・過大計上3件・施策指標1件の測定不能を検出</t>
+          <t>第3章を「第4次障がい者計画の推進状況（参考）」から「計画の基本理念・基本目標及び施策体系」へ再構成。第8期で加わる視点と施策体系の対応表を新設し、仕様書4-Ⅱ(5)①②を措置</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_現行計画評価.xlsx</t>
+          <t>北塩原村_骨子案_修正版.docx</t>
         </is>
       </c>
     </row>
@@ -5201,17 +5201,17 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>資料受領</t>
+          <t>評価</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>現行計画本編・アンケート調査結果報告書・概要版を受領。年齢3区分別人口5年分、前回調査の内訳（発送164人・回収95人）、成果目標の設定根拠が確定。将来推計・給付費の記載がないことを一次確認</t>
+          <t>現行計画評価ブックを作成。令和3〜5年度の見込量と実績を突合し、計上漏れ2件・過大計上3件・施策指標1件の測定不能を検出</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>現行計画本編（3379.pdf）／調査結果報告書（3380.pdf）／概要版（3388.pdf）</t>
+          <t>北塩原村_現行計画評価.xlsx</t>
         </is>
       </c>
     </row>
@@ -5223,17 +5223,17 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>進捗管理</t>
+          <t>資料受領</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>業務進捗管理ブックを新規作成。仕様書条項別の進捗台帳、村資料受領状況、課題・リスクを一本化</t>
+          <t>現行計画本編・アンケート調査結果報告書・概要版を受領。年齢3区分別人口5年分、前回調査の内訳（発送164人・回収95人）、成果目標の設定根拠が確定。将来推計・給付費の記載がないことを一次確認</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_業務進捗管理.xlsx</t>
+          <t>現行計画本編（3379.pdf）／調査結果報告書（3380.pdf）／概要版（3388.pdf）</t>
         </is>
       </c>
     </row>
@@ -5245,17 +5245,17 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>推計方法</t>
+          <t>進捗管理</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量を個別積上げ方式へ切替。計画素案に第5章1（見込量の推計方法）・第5章2（年齢到達に伴うサービスの移行）を新設</t>
+          <t>業務進捗管理ブックを新規作成。仕様書条項別の進捗台帳、村資料受領状況、課題・リスクを一本化</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_サービス見込量.xlsx／北塩原村_骨子案_修正版.docx</t>
+          <t>北塩原村_業務進捗管理.xlsx</t>
         </is>
       </c>
     </row>
@@ -5267,17 +5267,17 @@
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>調査</t>
+          <t>推計方法</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>年齢到達による給付の終了・移行を調査。骨子案に65歳・18歳の記述が0件、障がい者票に介護保険の設問がないことを確認</t>
+          <t>サービス見込量を個別積上げ方式へ切替。計画素案に第5章1（見込量の推計方法）・第5章2（年齢到達に伴うサービスの移行）を新設</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_年齢到達による給付移行_調査報告.md</t>
+          <t>北塩原村_サービス見込量.xlsx／北塩原村_骨子案_修正版.docx</t>
         </is>
       </c>
     </row>
@@ -5289,17 +5289,17 @@
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>検証</t>
+          <t>調査</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>推計方法のレッドチーム検証。時点表記の1年ずれ、方法Aの予測区間、方法Bの分母感度、過去稿の記載と計算の不一致を検出・修正</t>
+          <t>年齢到達による給付の終了・移行を調査。骨子案に65歳・18歳の記述が0件、障がい者票に介護保険の設問がないことを確認</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_推計方法_レッドチーム検証.md</t>
+          <t>北塩原村_年齢到達による給付移行_調査報告.md</t>
         </is>
       </c>
     </row>
@@ -5311,17 +5311,17 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>計画素案</t>
+          <t>検証</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>骨子案を正本とし、手帳将来推計・最新人口・財源構成・こども家庭センターを移植</t>
+          <t>推計方法のレッドチーム検証。時点表記の1年ずれ、方法Aの予測区間、方法Bの分母感度、過去稿の記載と計算の不一致を検出・修正</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_骨子案_修正版.docx</t>
+          <t>北塩原村_推計方法_レッドチーム検証.md</t>
         </is>
       </c>
     </row>
@@ -5333,17 +5333,17 @@
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
-          <t>レビュー</t>
+          <t>計画素案</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>骨子案★版と計画素案第9稿を比較し、正本を骨子案に決定</t>
+          <t>骨子案を正本とし、手帳将来推計・最新人口・財源構成・こども家庭センターを移植</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_骨子案_計画素案第9稿_比較レビュー.md</t>
+          <t>北塩原村_骨子案_修正版.docx</t>
         </is>
       </c>
     </row>
@@ -5355,91 +5355,107 @@
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>受注整理</t>
+          <t>レビュー</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>仕様書・議事録・成果物を突合し受注内容を整理</t>
+          <t>骨子案★版と計画素案第9稿を比較し、正本を骨子案に決定</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_第8期障がい福祉計画_受注内容整理.md</t>
+          <t>北塩原村_骨子案_計画素案第9稿_比較レビュー.md</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>調査票</t>
+          <t>受注整理</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>0728版アンケート調査票のレビュー（障がい者52問・障がい児51問）</t>
+          <t>仕様書・議事録・成果物を突合し受注内容を整理</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>0728北塩原村_障がい福祉／障がい児福祉アンケート調査票.docx</t>
+          <t>北塩原村_第8期障がい福祉計画_受注内容整理.md</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>障がいサービス給付実績（令和2〜7年度）を整理</t>
+          <t>0728版アンケート調査票のレビュー（障がい者52問・障がい児51問）</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_障がいサービス給付実績_整理版.xlsx</t>
+          <t>0728北塩原村_障がい福祉／障がい児福祉アンケート調査票.docx</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>障がいサービス給付実績（令和2〜7年度）を整理</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>北塩原村_障がいサービス給付実績_整理版.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>打合せ</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>北塩原村役場にて打合せ。アンケート実施設計を決定</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>議事録</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="37" t="n"/>
-      <c r="B18" s="38" t="n"/>
-      <c r="C18" s="39" t="n"/>
-      <c r="D18" s="39" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="37" t="n"/>
@@ -5470,6 +5486,12 @@
       <c r="B23" s="38" t="n"/>
       <c r="C23" s="39" t="n"/>
       <c r="D23" s="39" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="n"/>
+      <c r="B24" s="38" t="n"/>
+      <c r="C24" s="39" t="n"/>
+      <c r="D24" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_仕様書別進捗'!$A$5:$I$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>骨子案 第1章4（基本指針改正16項目、法定雇用率2.7%）／年齢到達による給付移行 調査報告／現行計画本編 第4章1（第7期の基本指針見直し）</t>
+          <t>骨子案 第1章4（基本指針改正16項目、法定雇用率2.7%）／年齢到達による給付移行 調査報告／現行計画本編 第4章1（第7期の基本指針見直し）／国基準数値 原典照合結果／告示本文・新旧対照表・改正後概要（source/基本指針）／令和8年度報酬改定資料（source/報酬改定）</t>
         </is>
       </c>
       <c r="E17" s="33" t="inlineStr">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="F17" s="9" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G17" s="32" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>骨子案が引用する国基準数値（319.3日、1.31倍、1.47倍等）を告示第4号の別表と照合する</t>
+          <t>国基準数値11件を告示第4号の本文・別表と照合済み（誤り1件・補足4件・欠落6件を骨子案修正版へ反映）。残るは福島県 第8期計画の公表待ち（別表第四による長期入院患者の基盤整備量、心のサポーター目標）</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3890,215 +3890,215 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
+          <t>本村の過疎区分（全部過疎／一部過疎／みなし過疎）</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>基本指針 別表第五の適用判定に用いる。総務省の過疎地域市町村一覧で確認できる</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>サービス見込量 12_別表第五判定</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G6" s="37" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>福島県の長期入院患者に係る基盤整備量（利用者数）</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>県が基本指針 別表第四の三の項の式により算定した令和11年度末の値。市町村はこれを勘案して当該区域の基盤整備量を定めなければならない（別表第二 三の項）</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>骨子案修正版 第4章(2)</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G7" s="37" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>令和6年度の一般就労移行実績・就労定着支援利用実績</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>成果目標の倍率（全体1.31倍、就労移行支援1.14倍、A型おおむね1.52倍、B型おおむね1.67倍、就労定着支援1.47倍）の基準値。事業種別ごとに必要</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>骨子案修正版 第4章(3)</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G8" s="37" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>第7期計画の令和8年度目標の達成見込み</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>未達の場合、未達成割合を令和11年度目標に上乗せする規定がある（第二 一・三）。本村は地域移行0人・削減0人が目標のため、達成／未達の整理が必要</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>骨子案修正版 第4章(1)(3)</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G9" s="37" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>年齢別・サービス別の匿名利用者一覧</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>利用者番号、生年月、障害支援区分、利用中のサービス、月利用日数・時間。氏名不要</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>サービス見込量 02・03・04</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="G6" s="37" t="n"/>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="G10" s="37" t="n"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>サービス別の支給決定者数（実人数）</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>請求件数ではなく実人数。計画相談支援は請求と実人数が一致しないため特に必要</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>サービス見込量 03・04</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="G7" s="37" t="n"/>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="G11" s="37" t="n"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>年齢階級別の手帳所持者数・人口</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>身体は0〜17／18〜39／40〜64／65〜74／75歳以上、療育・精神は18歳未満／18〜64／65歳以上</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>将来推計 05</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G8" s="37" t="n"/>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>令和6・7年度実績、令和8年度見込</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>成果目標、サービス別利用者数・利用量、給付費、地域生活支援事業、相談件数</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>前回計画評価／サービス見込量／財源構成案</t>
-        </is>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F9" s="26" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="n"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>発送対象者数（重複除外後）</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>仕様書の約190人の内訳と、現行計画156人との差の理由</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>契約管理5／アンケート発送設計</t>
-        </is>
-      </c>
-      <c r="E10" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="n"/>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>宛名ラベルシール</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>仕様書Ⅰ(1)により委託者が抽出し提供</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>アンケート発送</t>
-        </is>
-      </c>
-      <c r="E11" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F11" s="26" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="n"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>特別支援学校・特別支援学級の在籍者</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>学年、卒業予定年度、卒業後の進路。令和6〜7年度に卒業した方の現在の利用状況も含む</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>サービス見込量 02・03</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -4121,17 +4121,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>令和9〜11年度の65歳到達者</t>
+          <t>令和6・7年度実績、令和8年度見込</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>到達年度、現在利用しているサービス、月量</t>
+          <t>成果目標、サービス別利用者数・利用量、給付費、地域生活支援事業、相談件数</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 02・06</t>
+          <t>前回計画評価／サービス見込量／財源構成案</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
@@ -4147,34 +4147,34 @@
       <c r="G13" s="37" t="n"/>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>前回調査の調査結果報告書</t>
+          <t>発送対象者数（重複除外後）</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>発送164人・回収95人・回収率57.9%。設問別の集計結果を収録</t>
+          <t>仕様書の約190人の内訳と、現行計画156人との差の理由</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>アンケート集計設計・経年比較</t>
-        </is>
-      </c>
-      <c r="E14" s="36" t="inlineStr">
-        <is>
-          <t>受領済</t>
+          <t>契約管理5／アンケート発送設計</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G14" s="37" t="n"/>
@@ -4187,17 +4187,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>小規模公表基準</t>
+          <t>宛名ラベルシール</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>n&lt;5の秘匿、地区別・障がい種別クロスの扱い</t>
+          <t>仕様書Ⅰ(1)により委託者が抽出し提供</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>アンケート集計・報告書</t>
+          <t>アンケート発送</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="F15" s="26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G15" s="37" t="n"/>
@@ -4220,17 +4220,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉関係の歳入歳出決算</t>
+          <t>特別支援学校・特別支援学級の在籍者</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>自立支援給付費負担金、障害児施設給付費負担金、地域生活支援事業費補助金の交付額と村負担</t>
+          <t>学年、卒業予定年度、卒業後の進路。令和6〜7年度に卒業した方の現在の利用状況も含む</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>財源構成案 04・06・07</t>
+          <t>サービス見込量 02・03</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G16" s="37" t="n"/>
@@ -4253,17 +4253,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>令和6・7年度の障害児給付費の変動理由</t>
+          <t>令和9〜11年度の65歳到達者</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>児童発達支援23件→1件、放課後等デイ12件→27件の理由。受給者単位で就学移行かを確認</t>
+          <t>到達年度、現在利用しているサービス、月量</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 04／計画本文</t>
+          <t>サービス見込量 02・06</t>
         </is>
       </c>
       <c r="E17" s="27" t="inlineStr">
@@ -4286,17 +4286,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>現行計画本編（第4次障がい者計画・第7期・第3期）</t>
+          <t>前回調査の調査結果報告書</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>本編63頁、アンケート調査結果報告書69頁、概要版4頁。令和6年3月策定</t>
+          <t>発送164人・回収95人・回収率57.9%。設問別の集計結果を収録</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>全体（年齢3区分別人口・前回調査の内訳を反映済み）</t>
+          <t>アンケート集計設計・経年比較</t>
         </is>
       </c>
       <c r="E18" s="36" t="inlineStr">
@@ -4312,24 +4312,24 @@
       <c r="G18" s="37" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>圏域事業所の受入可能性</t>
+          <t>小規模公表基準</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>定員、空き、送迎範囲、受入可否。介護保険事業所の共生型サービス指定の有無を含む</t>
+          <t>n&lt;5の秘匿、地区別・障がい種別クロスの扱い</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 08</t>
+          <t>アンケート集計・報告書</t>
         </is>
       </c>
       <c r="E19" s="27" t="inlineStr">
@@ -4339,73 +4339,73 @@
       </c>
       <c r="F19" s="26" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G19" s="37" t="n"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>障がい福祉関係の歳入歳出決算</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>自立支援給付費負担金、障害児施設給付費負担金、地域生活支援事業費補助金の交付額と村負担</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>財源構成案 04・06・07</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="G19" s="37" t="n"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>医療的ケア児者・地域生活支援拠点・個別避難計画の実態</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>対象者数、支援内容、拠点の検証会・緊急対応、名簿・計画の作成状況</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>計画本文 第4章・第6章</t>
-        </is>
-      </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="G20" s="37" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>令和6・7年度の障害児給付費の変動理由</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>児童発達支援23件→1件、放課後等デイ12件→27件の理由。受給者単位で就学移行かを確認</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>サービス見込量 04／計画本文</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="G20" s="37" t="n"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>関連計画との整合確認</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>計画本文 第1章・第7章</t>
-        </is>
-      </c>
-      <c r="E21" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
       <c r="F21" s="26" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G21" s="37" t="n"/>
@@ -4413,32 +4413,32 @@
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="30" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>40歳以上65歳未満の特定疾病該当者</t>
+          <t>現行計画本編（第4次障がい者計画・第7期・第3期）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+          <t>本編63頁、アンケート調査結果報告書69頁、概要版4頁。令和6年3月策定</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>サービス見込量 02</t>
-        </is>
-      </c>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+          <t>全体（年齢3区分別人口・前回調査の内訳を反映済み）</t>
+        </is>
+      </c>
+      <c r="E22" s="36" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G22" s="37" t="n"/>
@@ -4451,44 +4451,176 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>圏域事業所の受入可能性</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>定員、空き、送迎範囲、受入可否。介護保険事業所の共生型サービス指定の有無を含む</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>サービス見込量 08</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G23" s="37" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>医療的ケア児者・地域生活支援拠点・個別避難計画の実態</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>対象者数、支援内容、拠点の検証会・緊急対応、名簿・計画の作成状況</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>計画本文 第4章・第6章</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G24" s="37" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>関連計画との整合確認</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>計画本文 第1章・第7章</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G25" s="37" t="n"/>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>40歳以上65歳未満の特定疾病該当者</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>サービス見込量 02</t>
+        </is>
+      </c>
+      <c r="E26" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G26" s="37" t="n"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
           <t>自立支援協議会の委員名簿</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>任期・氏名・所属・役職</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>計画書 資料編</t>
         </is>
       </c>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="E27" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="F27" s="26" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="G23" s="37" t="n"/>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>未受領：18件（うち最優先3件、高9件）。最優先の3件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。</t>
+      <c r="G27" s="37" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>未受領：22件（うち最優先3件、高9件）。最優先の3件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G23"/>
+  <autoFilter ref="A5:G27"/>
   <mergeCells count="3">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4500,7 +4632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4796,9 +4928,9 @@
           <t>品質</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -4808,49 +4940,49 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>319.3日、1.31倍、1.47倍等の数値がそのまま印刷される。第7期の数値が混在するおそれ</t>
+          <t>【解消】告示第4号の本文・別表と11件を照合。319.3日・1.31倍・1.47倍はいずれも第8期の正しい数値。誤りは就労定着支援の基準（令和6年度末→令和6年度）1件。むしろ欠落6件（B型1.67倍等の事業種別目標、精神病床1年以上長期入院患者数ほか）が問題だった</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>告示第4号の別表と1件ずつ照合する</t>
+          <t>骨子案修正版 第4章へ反映済み。改正後概要と告示本文で表記が異なる箇所は告示本文に従う</t>
         </is>
       </c>
       <c r="G12" s="30" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="32" t="inlineStr">
         <is>
-          <t>R-8</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
-          <t>品質</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>推計</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>障がい児版調査票のルビ構造により本文が欠落して見える箇所がある</t>
+          <t>基本指針 別表第五（地域差是正）の適用関係が未確定</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>問1〜問15で語句が欠けて抽出される。Word表示上は正常な可能性もある</t>
+          <t>第8期で新設。全部過疎市町村でなく、かつサービス利用者割合が上位25%以内の市町村は、全国の伸び率を用いた算定方法が基本となる。該当すると個別積上げ方式が原則から外れ、採用するには必要性及び根拠を計画本文に明記する必要がある</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Word上でルビなしテキストとして読んで意味が通るかを確認する</t>
+          <t>総務省の過疎地域市町村一覧で本村の過疎区分を確認する。全部過疎であれば適用対象外となり、現在の設計のまま進められる</t>
         </is>
       </c>
       <c r="G13" s="32" t="inlineStr">
@@ -4862,12 +4994,12 @@
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>R-9</t>
+          <t>R-13</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>財源</t>
         </is>
       </c>
       <c r="C14" s="34" t="inlineStr">
@@ -4877,101 +5009,175 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>障がい者票に介護保険・65歳到達に関する設問がない</t>
+          <t>令和8年度・令和9年度の報酬改定により単価前提が動く</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない</t>
+          <t>令和8年6月施行の処遇改善加算拡充（月1.0万円＝3.3%＋上乗せ1.0%）とB型基本報酬区分見直し。さらに令和9年度報酬改定が見込まれ、計画期間の初年度に当たる。令和7年度実績単価を据え置くと給付費推計が実勢とずれる</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳での確認に一本化する</t>
+          <t>財源構成案 08シートに改定率パラメータを設置済み。改定内容の確定後に入力する</t>
         </is>
       </c>
       <c r="G14" s="30" t="inlineStr">
         <is>
-          <t>判断待ち</t>
+          <t>対応中</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="32" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-8</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>品質</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の施策目標のうち1指標が測定できない</t>
+          <t>障がい児版調査票のルビ構造により本文が欠落して見える箇所がある</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない</t>
+          <t>問1〜問15で語句が欠けて抽出される。Word表示上は正常な可能性もある</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>発送前であれば問13の後に外出目的の設問を追加するか、問45の選択肢を前回に揃える。発送後であれば別の把握方法へ切り替える旨を村と協議する</t>
+          <t>Word上でルビなしテキストとして読んで意味が通るかを確認する</t>
         </is>
       </c>
       <c r="G15" s="32" t="inlineStr">
         <is>
-          <t>判断待ち</t>
+          <t>対応中</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
+          <t>R-9</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>障がい者票に介護保険・65歳到達に関する設問がない</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳での確認に一本化する</t>
+        </is>
+      </c>
+      <c r="G16" s="30" t="inlineStr">
+        <is>
+          <t>判断待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>R-11</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>第4次障がい者計画の施策目標のうち1指標が測定できない</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>発送前であれば問13の後に外出目的の設問を追加するか、問45の選択肢を前回に揃える。発送後であれば別の把握方法へ切り替える旨を村と協議する</t>
+        </is>
+      </c>
+      <c r="G17" s="32" t="inlineStr">
+        <is>
+          <t>判断待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>供給</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>圏域事業所の受入可能量が見込量の上限になる</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>村内に事業所がなく、送迎・人材・定員が制約となる</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>圏域事業所へ照会し、利用希望量と利用可能量を分けて管理する</t>
         </is>
       </c>
-      <c r="G16" s="30" t="inlineStr">
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G16"/>
+  <autoFilter ref="A5:G18"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_仕様書別進捗'!$A$5:$I$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3819,7 +3819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>基本指針 別表第五の適用判定に用いる。総務省の過疎地域市町村一覧で確認できる</t>
+          <t>【受領済み】福島県「県内の過疎・中山間地域の指定状況」（令和7年4月1日現在）。過疎法第2条により全域が過疎地域。県条例の中山間地域にも全域が該当</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3903,14 +3903,14 @@
           <t>サービス見込量 12_別表第五判定</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G6" s="37" t="n"/>
@@ -3923,17 +3923,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>福島県の長期入院患者に係る基盤整備量（利用者数）</t>
+          <t>圏域事業所の制度活用状況</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>県が基本指針 別表第四の三の項の式により算定した令和11年度末の値。市町村はこれを勘案して当該区域の基盤整備量を定めなければならない（別表第二 三の項）</t>
+          <t>共生型サービスの指定の有無、多機能型・従たる事業所の設置可能性、介護保険事業所（訪問介護・居宅介護支援）の居宅介護指定取得の意向</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>骨子案修正版 第4章(2)</t>
+          <t>骨子案修正版 第5章8／サービス見込量 08</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">
@@ -3956,93 +3956,93 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>福島県の長期入院患者に係る基盤整備量（利用者数）</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>県が基本指針 別表第四の三の項の式により算定した令和11年度末の値。市町村はこれを勘案して当該区域の基盤整備量を定めなければならない（別表第二 三の項）</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>骨子案修正版 第4章(2)</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G8" s="37" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
           <t>令和6年度の一般就労移行実績・就労定着支援利用実績</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>成果目標の倍率（全体1.31倍、就労移行支援1.14倍、A型おおむね1.52倍、B型おおむね1.67倍、就労定着支援1.47倍）の基準値。事業種別ごとに必要</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>骨子案修正版 第4章(3)</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G8" s="37" t="n"/>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="G9" s="37" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>第7期計画の令和8年度目標の達成見込み</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>未達の場合、未達成割合を令和11年度目標に上乗せする規定がある（第二 一・三）。本村は地域移行0人・削減0人が目標のため、達成／未達の整理が必要</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>骨子案修正版 第4章(1)(3)</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="n"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>最優先</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>年齢別・サービス別の匿名利用者一覧</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>利用者番号、生年月、障害支援区分、利用中のサービス、月利用日数・時間。氏名不要</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>サービス見込量 02・03・04</t>
-        </is>
-      </c>
-      <c r="E10" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G10" s="37" t="n"/>
@@ -4055,17 +4055,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>サービス別の支給決定者数（実人数）</t>
+          <t>年齢別・サービス別の匿名利用者一覧</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>請求件数ではなく実人数。計画相談支援は請求と実人数が一致しないため特に必要</t>
+          <t>利用者番号、生年月、障害支援区分、利用中のサービス、月利用日数・時間。氏名不要</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 03・04</t>
+          <t>サービス見込量 02・03・04</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
@@ -4088,50 +4088,50 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
+          <t>サービス別の支給決定者数（実人数）</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>請求件数ではなく実人数。計画相談支援は請求と実人数が一致しないため特に必要</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>サービス見込量 03・04</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="n"/>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
           <t>年齢階級別の手帳所持者数・人口</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>身体は0〜17／18〜39／40〜64／65〜74／75歳以上、療育・精神は18歳未満／18〜64／65歳以上</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>将来推計 05</t>
-        </is>
-      </c>
-      <c r="E12" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="n"/>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>令和6・7年度実績、令和8年度見込</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>成果目標、サービス別利用者数・利用量、給付費、地域生活支援事業、相談件数</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>前回計画評価／サービス見込量／財源構成案</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
@@ -4154,17 +4154,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>発送対象者数（重複除外後）</t>
+          <t>令和6・7年度実績、令和8年度見込</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>仕様書の約190人の内訳と、現行計画156人との差の理由</t>
+          <t>成果目標、サービス別利用者数・利用量、給付費、地域生活支援事業、相談件数</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>契約管理5／アンケート発送設計</t>
+          <t>前回計画評価／サービス見込量／財源構成案</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G14" s="37" t="n"/>
@@ -4187,17 +4187,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>宛名ラベルシール</t>
+          <t>発送対象者数（重複除外後）</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>仕様書Ⅰ(1)により委託者が抽出し提供</t>
+          <t>仕様書の約190人の内訳と、現行計画156人との差の理由</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>アンケート発送</t>
+          <t>契約管理5／アンケート発送設計</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
@@ -4220,17 +4220,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>特別支援学校・特別支援学級の在籍者</t>
+          <t>宛名ラベルシール</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>学年、卒業予定年度、卒業後の進路。令和6〜7年度に卒業した方の現在の利用状況も含む</t>
+          <t>仕様書Ⅰ(1)により委託者が抽出し提供</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>サービス見込量 02・03</t>
+          <t>アンケート発送</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G16" s="37" t="n"/>
@@ -4253,93 +4253,93 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
+          <t>特別支援学校・特別支援学級の在籍者</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>学年、卒業予定年度、卒業後の進路。令和6〜7年度に卒業した方の現在の利用状況も含む</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>サービス見込量 02・03</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G17" s="37" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>令和9〜11年度の65歳到達者</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>到達年度、現在利用しているサービス、月量</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>サービス見込量 02・06</t>
         </is>
       </c>
-      <c r="E17" s="27" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G17" s="37" t="n"/>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="G18" s="37" t="n"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>前回調査の調査結果報告書</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>発送164人・回収95人・回収率57.9%。設問別の集計結果を収録</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>アンケート集計設計・経年比較</t>
         </is>
       </c>
-      <c r="E18" s="36" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F19" s="26" t="inlineStr">
         <is>
           <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G18" s="37" t="n"/>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>小規模公表基準</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>n&lt;5の秘匿、地区別・障がい種別クロスの扱い</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>アンケート集計・報告書</t>
-        </is>
-      </c>
-      <c r="E19" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F19" s="26" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G19" s="37" t="n"/>
@@ -4352,17 +4352,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉関係の歳入歳出決算</t>
+          <t>小規模公表基準</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>自立支援給付費負担金、障害児施設給付費負担金、地域生活支援事業費補助金の交付額と村負担</t>
+          <t>n&lt;5の秘匿、地区別・障がい種別クロスの扱い</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>財源構成案 04・06・07</t>
+          <t>アンケート集計・報告書</t>
         </is>
       </c>
       <c r="E20" s="27" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G20" s="37" t="n"/>
@@ -4385,60 +4385,60 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
+          <t>障がい福祉関係の歳入歳出決算</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>自立支援給付費負担金、障害児施設給付費負担金、地域生活支援事業費補助金の交付額と村負担</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>財源構成案 04・06・07</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G21" s="37" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t>令和6・7年度の障害児給付費の変動理由</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>児童発達支援23件→1件、放課後等デイ12件→27件の理由。受給者単位で就学移行かを確認</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>サービス見込量 04／計画本文</t>
         </is>
       </c>
-      <c r="E21" s="27" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G21" s="37" t="n"/>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>現行計画本編（第4次障がい者計画・第7期・第3期）</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>本編63頁、アンケート調査結果報告書69頁、概要版4頁。令和6年3月策定</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>全体（年齢3区分別人口・前回調査の内訳を反映済み）</t>
-        </is>
-      </c>
-      <c r="E22" s="36" t="inlineStr">
-        <is>
-          <t>受領済</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G22" s="37" t="n"/>
@@ -4446,32 +4446,32 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="32" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>圏域事業所の受入可能性</t>
+          <t>現行計画本編（第4次障がい者計画・第7期・第3期）</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>定員、空き、送迎範囲、受入可否。介護保険事業所の共生型サービス指定の有無を含む</t>
+          <t>本編63頁、アンケート調査結果報告書69頁、概要版4頁。令和6年3月策定</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 08</t>
-        </is>
-      </c>
-      <c r="E23" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+          <t>全体（年齢3区分別人口・前回調査の内訳を反映済み）</t>
+        </is>
+      </c>
+      <c r="E23" s="36" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
       <c r="F23" s="26" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G23" s="37" t="n"/>
@@ -4484,17 +4484,17 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>医療的ケア児者・地域生活支援拠点・個別避難計画の実態</t>
+          <t>圏域事業所の受入可能性</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>対象者数、支援内容、拠点の検証会・緊急対応、名簿・計画の作成状況</t>
+          <t>定員、空き、送迎範囲、受入可否。介護保険事業所の共生型サービス指定の有無を含む</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>計画本文 第4章・第6章</t>
+          <t>サービス見込量 08</t>
         </is>
       </c>
       <c r="E24" s="27" t="inlineStr">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
+          <t>医療的ケア児者・地域生活支援拠点・個別避難計画の実態</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>関連計画との整合確認</t>
+          <t>対象者数、支援内容、拠点の検証会・緊急対応、名簿・計画の作成状況</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>計画本文 第1章・第7章</t>
+          <t>計画本文 第4章・第6章</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
@@ -4550,17 +4550,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>40歳以上65歳未満の特定疾病該当者</t>
+          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+          <t>関連計画との整合確認</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>サービス見込量 02</t>
+          <t>計画本文 第1章・第7章</t>
         </is>
       </c>
       <c r="E26" s="27" t="inlineStr">
@@ -4583,44 +4583,77 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
+          <t>40歳以上65歳未満の特定疾病該当者</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>サービス見込量 02</t>
+        </is>
+      </c>
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G27" s="37" t="n"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>自立支援協議会の委員名簿</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>任期・氏名・所属・役職</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>計画書 資料編</t>
         </is>
       </c>
-      <c r="E27" s="27" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F27" s="26" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="G27" s="37" t="n"/>
-    </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>未受領：22件（うち最優先3件、高9件）。最優先の3件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。</t>
+      <c r="G28" s="37" t="n"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>未受領：23件（うち最優先3件、高9件）。最優先の3件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G27"/>
+  <autoFilter ref="A5:G28"/>
   <mergeCells count="3">
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A29:G29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4632,7 +4665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4965,9 +4998,9 @@
           <t>推計</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -4977,49 +5010,49 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>第8期で新設。全部過疎市町村でなく、かつサービス利用者割合が上位25%以内の市町村は、全国の伸び率を用いた算定方法が基本となる。該当すると個別積上げ方式が原則から外れ、採用するには必要性及び根拠を計画本文に明記する必要がある</t>
+          <t>【解消】福島県「県内の過疎・中山間地域の指定状況」（令和7年4月1日現在）により、本村は過疎法第2条により全域が過疎地域に該当することを確認。別表第五 一の項⑴「全部過疎市町村ではないこと」を満たさず適用対象外。個別積上げ方式を原則どおり採用できる</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>総務省の過疎地域市町村一覧で本村の過疎区分を確認する。全部過疎であれば適用対象外となり、現在の設計のまま進められる</t>
+          <t>骨子案修正版 第5章1及びサービス見込量ブック 12 へ反映済み</t>
         </is>
       </c>
       <c r="G13" s="32" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>完了</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>財源</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>提供体制</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>令和8年度・令和9年度の報酬改定により単価前提が動く</t>
+          <t>村内に障がい福祉サービス事業所が1か所もない</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>令和8年6月施行の処遇改善加算拡充（月1.0万円＝3.3%＋上乗せ1.0%）とB型基本報酬区分見直し。さらに令和9年度報酬改定が見込まれ、計画期間の初年度に当たる。令和7年度実績単価を据え置くと給付費推計が実勢とずれる</t>
+          <t>基本指針 第三の二の2(二)は、訪問系サービス及び指定通所支援について「各市町村において事業を実施する事業所を最低一箇所確保できるよう努める」としている。本村は0か所であり、圏域及び近隣市の事業所に全面的に依存している。事業所の撤退・受入制限がそのまま利用不能につながる</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>財源構成案 08シートに改定率パラメータを設置済み。改定内容の確定後に入力する</t>
+          <t>告示が示す工夫（介護保険事業所への居宅介護指定の働きかけ、共生型サービスの周知、基準該当障害福祉サービス、多機能型・従たる事業所）を骨子案修正版 第5章8 に位置づけた。圏域4町村の担当者会議で各制度の活用可能性を確認する</t>
         </is>
       </c>
       <c r="G14" s="30" t="inlineStr">
@@ -5031,12 +5064,12 @@
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="32" t="inlineStr">
         <is>
-          <t>R-8</t>
+          <t>R-13</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>品質</t>
+          <t>財源</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
@@ -5046,17 +5079,17 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>障がい児版調査票のルビ構造により本文が欠落して見える箇所がある</t>
+          <t>令和8年度・令和9年度の報酬改定により単価前提が動く</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>問1〜問15で語句が欠けて抽出される。Word表示上は正常な可能性もある</t>
+          <t>令和8年6月施行の処遇改善加算拡充（月1.0万円＝3.3%＋上乗せ1.0%）とB型基本報酬区分見直し。さらに令和9年度報酬改定が見込まれ、計画期間の初年度に当たる。令和7年度実績単価を据え置くと給付費推計が実勢とずれる</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Word上でルビなしテキストとして読んで意味が通るかを確認する</t>
+          <t>財源構成案 08シートに改定率パラメータを設置済み。改定内容の確定後に入力する</t>
         </is>
       </c>
       <c r="G15" s="32" t="inlineStr">
@@ -5068,12 +5101,12 @@
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>R-9</t>
+          <t>R-8</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>品質</t>
         </is>
       </c>
       <c r="C16" s="34" t="inlineStr">
@@ -5083,29 +5116,29 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>障がい者票に介護保険・65歳到達に関する設問がない</t>
+          <t>障がい児版調査票のルビ構造により本文が欠落して見える箇所がある</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない</t>
+          <t>問1〜問15で語句が欠けて抽出される。Word表示上は正常な可能性もある</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳での確認に一本化する</t>
+          <t>Word上でルビなしテキストとして読んで意味が通るかを確認する</t>
         </is>
       </c>
       <c r="G16" s="30" t="inlineStr">
         <is>
-          <t>判断待ち</t>
+          <t>対応中</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="32" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-9</t>
         </is>
       </c>
       <c r="B17" s="32" t="inlineStr">
@@ -5113,24 +5146,24 @@
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C17" s="27" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の施策目標のうち1指標が測定できない</t>
+          <t>障がい者票に介護保険・65歳到達に関する設問がない</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない</t>
+          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>発送前であれば問13の後に外出目的の設問を追加するか、問45の選択肢を前回に揃える。発送後であれば別の把握方法へ切り替える旨を村と協議する</t>
+          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳での確認に一本化する</t>
         </is>
       </c>
       <c r="G17" s="32" t="inlineStr">
@@ -5142,42 +5175,79 @@
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="30" t="inlineStr">
         <is>
+          <t>R-11</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>第4次障がい者計画の施策目標のうち1指標が測定できない</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>発送前であれば問13の後に外出目的の設問を追加するか、問45の選択肢を前回に揃える。発送後であれば別の把握方法へ切り替える旨を村と協議する</t>
+        </is>
+      </c>
+      <c r="G18" s="30" t="inlineStr">
+        <is>
+          <t>判断待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>供給</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>圏域事業所の受入可能量が見込量の上限になる</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>村内に事業所がなく、送迎・人材・定員が制約となる</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>圏域事業所へ照会し、利用希望量と利用可能量を分けて管理する</t>
         </is>
       </c>
-      <c r="G18" s="30" t="inlineStr">
+      <c r="G19" s="32" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G18"/>
+  <autoFilter ref="A5:G19"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_仕様書別進捗'!$A$5:$I$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3819,7 +3819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3949,19 +3949,19 @@
       <c r="G7" s="37" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>最優先</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>福島県の長期入院患者に係る基盤整備量（利用者数）</t>
+          <t>令和7年度末時点の1年以上長期入院者の実数</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>県が基本指針 別表第四の三の項の式により算定した令和11年度末の値。市町村はこれを勘案して当該区域の基盤整備量を定めなければならない（別表第二 三の項）</t>
+          <t>人数、年齢区分（65歳未満／65歳以上／75歳以上／40歳以上の認知症の別）、入院先、退院の可能性。現行計画の令和5年度5人が起点。村・会津保健所で確認</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G8" s="37" t="n"/>
@@ -3989,93 +3989,93 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
+          <t>福島県の長期入院患者に係る基盤整備量（利用者数）</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>県が基本指針 別表第四の三の項の式により算定した令和11年度末の値。県第7期計画は一・二の項に相当する長期在院者数（R8末目標 65歳未満898人・65歳以上1,656人）のみ掲載し三の項は無いため、県への個別照会が必要</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>骨子案修正版 第4章(2)</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>県照会中</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G9" s="37" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>令和6年度の一般就労移行実績・就労定着支援利用実績</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>成果目標の倍率（全体1.31倍、就労移行支援1.14倍、A型おおむね1.52倍、B型おおむね1.67倍、就労定着支援1.47倍）の基準値。事業種別ごとに必要</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>骨子案修正版 第4章(3)</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G9" s="37" t="n"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="G10" s="37" t="n"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>第7期計画の令和8年度目標の達成見込み</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>未達の場合、未達成割合を令和11年度目標に上乗せする規定がある（第二 一・三）。本村は地域移行0人・削減0人が目標のため、達成／未達の整理が必要</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>骨子案修正版 第4章(1)(3)</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="n"/>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>最優先</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>年齢別・サービス別の匿名利用者一覧</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>利用者番号、生年月、障害支援区分、利用中のサービス、月利用日数・時間。氏名不要</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>サービス見込量 02・03・04</t>
-        </is>
-      </c>
-      <c r="E11" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F11" s="26" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G11" s="37" t="n"/>
@@ -4088,17 +4088,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>サービス別の支給決定者数（実人数）</t>
+          <t>年齢別・サービス別の匿名利用者一覧</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>請求件数ではなく実人数。計画相談支援は請求と実人数が一致しないため特に必要</t>
+          <t>利用者番号、生年月、障害支援区分、利用中のサービス、月利用日数・時間。氏名不要</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>サービス見込量 03・04</t>
+          <t>サービス見込量 02・03・04</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -4121,50 +4121,50 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
+          <t>サービス別の支給決定者数（実人数）</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>請求件数ではなく実人数。計画相談支援は請求と実人数が一致しないため特に必要</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>サービス見込量 03・04</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
           <t>年齢階級別の手帳所持者数・人口</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>身体は0〜17／18〜39／40〜64／65〜74／75歳以上、療育・精神は18歳未満／18〜64／65歳以上</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>将来推計 05</t>
-        </is>
-      </c>
-      <c r="E13" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F13" s="26" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G13" s="37" t="n"/>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>令和6・7年度実績、令和8年度見込</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>成果目標、サービス別利用者数・利用量、給付費、地域生活支援事業、相談件数</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>前回計画評価／サービス見込量／財源構成案</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
@@ -4187,17 +4187,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>発送対象者数（重複除外後）</t>
+          <t>令和6・7年度実績、令和8年度見込</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>仕様書の約190人の内訳と、現行計画156人との差の理由</t>
+          <t>成果目標、サービス別利用者数・利用量、給付費、地域生活支援事業、相談件数</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>契約管理5／アンケート発送設計</t>
+          <t>前回計画評価／サービス見込量／財源構成案</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="F15" s="26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G15" s="37" t="n"/>
@@ -4220,17 +4220,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>宛名ラベルシール</t>
+          <t>発送対象者数（重複除外後）</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>仕様書Ⅰ(1)により委託者が抽出し提供</t>
+          <t>仕様書の約190人の内訳と、現行計画156人との差の理由</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>アンケート発送</t>
+          <t>契約管理5／アンケート発送設計</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
@@ -4253,17 +4253,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>特別支援学校・特別支援学級の在籍者</t>
+          <t>宛名ラベルシール</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>学年、卒業予定年度、卒業後の進路。令和6〜7年度に卒業した方の現在の利用状況も含む</t>
+          <t>仕様書Ⅰ(1)により委託者が抽出し提供</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 02・03</t>
+          <t>アンケート発送</t>
         </is>
       </c>
       <c r="E17" s="27" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="F17" s="26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G17" s="37" t="n"/>
@@ -4286,93 +4286,93 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>特別支援学校・特別支援学級の在籍者</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>学年、卒業予定年度、卒業後の進路。令和6〜7年度に卒業した方の現在の利用状況も含む</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>サービス見込量 02・03</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G18" s="37" t="n"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
           <t>令和9〜11年度の65歳到達者</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>到達年度、現在利用しているサービス、月量</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>サービス見込量 02・06</t>
         </is>
       </c>
-      <c r="E18" s="27" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F19" s="26" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G18" s="37" t="n"/>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="G19" s="37" t="n"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>前回調査の調査結果報告書</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>発送164人・回収95人・回収率57.9%。設問別の集計結果を収録</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>アンケート集計設計・経年比較</t>
         </is>
       </c>
-      <c r="E19" s="36" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G19" s="37" t="n"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>小規模公表基準</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>n&lt;5の秘匿、地区別・障がい種別クロスの扱い</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>アンケート集計・報告書</t>
-        </is>
-      </c>
-      <c r="E20" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G20" s="37" t="n"/>
@@ -4385,17 +4385,17 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>障がい福祉関係の歳入歳出決算</t>
+          <t>小規模公表基準</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>自立支援給付費負担金、障害児施設給付費負担金、地域生活支援事業費補助金の交付額と村負担</t>
+          <t>n&lt;5の秘匿、地区別・障がい種別クロスの扱い</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>財源構成案 04・06・07</t>
+          <t>アンケート集計・報告書</t>
         </is>
       </c>
       <c r="E21" s="27" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="F21" s="26" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G21" s="37" t="n"/>
@@ -4418,60 +4418,60 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
+          <t>障がい福祉関係の歳入歳出決算</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>自立支援給付費負担金、障害児施設給付費負担金、地域生活支援事業費補助金の交付額と村負担</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>財源構成案 04・06・07</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G22" s="37" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
           <t>令和6・7年度の障害児給付費の変動理由</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>児童発達支援23件→1件、放課後等デイ12件→27件の理由。受給者単位で就学移行かを確認</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>サービス見込量 04／計画本文</t>
         </is>
       </c>
-      <c r="E22" s="27" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F23" s="26" t="inlineStr">
         <is>
           <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G22" s="37" t="n"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>現行計画本編（第4次障がい者計画・第7期・第3期）</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>本編63頁、アンケート調査結果報告書69頁、概要版4頁。令和6年3月策定</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>全体（年齢3区分別人口・前回調査の内訳を反映済み）</t>
-        </is>
-      </c>
-      <c r="E23" s="36" t="inlineStr">
-        <is>
-          <t>受領済</t>
-        </is>
-      </c>
-      <c r="F23" s="26" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G23" s="37" t="n"/>
@@ -4479,32 +4479,32 @@
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>圏域事業所の受入可能性</t>
+          <t>現行計画本編（第4次障がい者計画・第7期・第3期）</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>定員、空き、送迎範囲、受入可否。介護保険事業所の共生型サービス指定の有無を含む</t>
+          <t>本編63頁、アンケート調査結果報告書69頁、概要版4頁。令和6年3月策定</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>サービス見込量 08</t>
-        </is>
-      </c>
-      <c r="E24" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+          <t>全体（年齢3区分別人口・前回調査の内訳を反映済み）</t>
+        </is>
+      </c>
+      <c r="E24" s="36" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G24" s="37" t="n"/>
@@ -4517,17 +4517,17 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>医療的ケア児者・地域生活支援拠点・個別避難計画の実態</t>
+          <t>圏域事業所の受入可能性</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>対象者数、支援内容、拠点の検証会・緊急対応、名簿・計画の作成状況</t>
+          <t>定員、空き、送迎範囲、受入可否。介護保険事業所の共生型サービス指定の有無を含む</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>計画本文 第4章・第6章</t>
+          <t>サービス見込量 08</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
@@ -4550,17 +4550,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
+          <t>医療的ケア児者・地域生活支援拠点・個別避難計画の実態</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>関連計画との整合確認</t>
+          <t>対象者数、支援内容、拠点の検証会・緊急対応、名簿・計画の作成状況</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>計画本文 第1章・第7章</t>
+          <t>計画本文 第4章・第6章</t>
         </is>
       </c>
       <c r="E26" s="27" t="inlineStr">
@@ -4583,17 +4583,17 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>40歳以上65歳未満の特定疾病該当者</t>
+          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+          <t>関連計画との整合確認</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 02</t>
+          <t>計画本文 第1章・第7章</t>
         </is>
       </c>
       <c r="E27" s="27" t="inlineStr">
@@ -4616,42 +4616,75 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
+          <t>40歳以上65歳未満の特定疾病該当者</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>サービス見込量 02</t>
+        </is>
+      </c>
+      <c r="E28" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G28" s="37" t="n"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
           <t>自立支援協議会の委員名簿</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>任期・氏名・所属・役職</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>計画書 資料編</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F29" s="26" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="G28" s="37" t="n"/>
-    </row>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>未受領：23件（うち最優先3件、高9件）。最優先の3件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。</t>
+      <c r="G29" s="37" t="n"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>未受領：24件（うち最優先3件、高9件）。最優先の3件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G28"/>
+  <autoFilter ref="A5:G29"/>
   <mergeCells count="3">
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -4665,7 +4698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5027,32 +5060,32 @@
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>提供体制</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>推計</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>村内に障がい福祉サービス事業所が1か所もない</t>
+          <t>国基準数値と福島県実績の系統が複数あり、どれを用いるかで目標値が変わる</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>基本指針 第三の二の2(二)は、訪問系サービス及び指定通所支援について「各市町村において事業を実施する事業所を最低一箇所確保できるよう努める」としている。本村は0か所であり、圏域及び近隣市の事業所に全面的に依存している。事業所の撤退・受入制限がそのまま利用不能につながる</t>
+          <t>平均生活日数はNDB通常集計327.1日・公費含む集計323.8日、1年以上入院患者数は県計画(630調査)2,808人・NDB通常2,449人・NDB公費2,758人・ReMHRAD(630調査R7)2,220人と、出典により値が異なる。告示のCが630調査の実人数かNDBの1日平均在院患者数かも特定できていない</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>告示が示す工夫（介護保険事業所への居宅介護指定の働きかけ、共生型サービスの周知、基準該当障害福祉サービス、多機能型・従たる事業所）を骨子案修正版 第5章8 に位置づけた。圏域4町村の担当者会議で各制度の活用可能性を確認する</t>
+          <t>国の算定要領を県経由で確認する。計画本文には出典と時点を必ず併記する</t>
         </is>
       </c>
       <c r="G14" s="30" t="inlineStr">
@@ -5064,32 +5097,32 @@
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="32" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>財源</t>
-        </is>
-      </c>
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>提供体制</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>令和8年度・令和9年度の報酬改定により単価前提が動く</t>
+          <t>村内に障がい福祉サービス事業所が1か所もない</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>令和8年6月施行の処遇改善加算拡充（月1.0万円＝3.3%＋上乗せ1.0%）とB型基本報酬区分見直し。さらに令和9年度報酬改定が見込まれ、計画期間の初年度に当たる。令和7年度実績単価を据え置くと給付費推計が実勢とずれる</t>
+          <t>基本指針 第三の二の2(二)は、訪問系サービス及び指定通所支援について「各市町村において事業を実施する事業所を最低一箇所確保できるよう努める」としている。本村は0か所であり、圏域及び近隣市の事業所に全面的に依存している。事業所の撤退・受入制限がそのまま利用不能につながる</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>財源構成案 08シートに改定率パラメータを設置済み。改定内容の確定後に入力する</t>
+          <t>告示が示す工夫（介護保険事業所への居宅介護指定の働きかけ、共生型サービスの周知、基準該当障害福祉サービス、多機能型・従たる事業所）を骨子案修正版 第5章8 に位置づけた。圏域4町村の担当者会議で各制度の活用可能性を確認する</t>
         </is>
       </c>
       <c r="G15" s="32" t="inlineStr">
@@ -5101,12 +5134,12 @@
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>R-8</t>
+          <t>R-13</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>品質</t>
+          <t>財源</t>
         </is>
       </c>
       <c r="C16" s="34" t="inlineStr">
@@ -5116,17 +5149,17 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>障がい児版調査票のルビ構造により本文が欠落して見える箇所がある</t>
+          <t>令和8年度・令和9年度の報酬改定により単価前提が動く</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>問1〜問15で語句が欠けて抽出される。Word表示上は正常な可能性もある</t>
+          <t>令和8年6月施行の処遇改善加算拡充（月1.0万円＝3.3%＋上乗せ1.0%）とB型基本報酬区分見直し。さらに令和9年度報酬改定が見込まれ、計画期間の初年度に当たる。令和7年度実績単価を据え置くと給付費推計が実勢とずれる</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Word上でルビなしテキストとして読んで意味が通るかを確認する</t>
+          <t>財源構成案 08シートに改定率パラメータを設置済み。改定内容の確定後に入力する</t>
         </is>
       </c>
       <c r="G16" s="30" t="inlineStr">
@@ -5138,12 +5171,12 @@
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="32" t="inlineStr">
         <is>
-          <t>R-9</t>
+          <t>R-8</t>
         </is>
       </c>
       <c r="B17" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>品質</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
@@ -5153,29 +5186,29 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>障がい者票に介護保険・65歳到達に関する設問がない</t>
+          <t>障がい児版調査票のルビ構造により本文が欠落して見える箇所がある</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない</t>
+          <t>問1〜問15で語句が欠けて抽出される。Word表示上は正常な可能性もある</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳での確認に一本化する</t>
+          <t>Word上でルビなしテキストとして読んで意味が通るかを確認する</t>
         </is>
       </c>
       <c r="G17" s="32" t="inlineStr">
         <is>
-          <t>判断待ち</t>
+          <t>対応中</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-9</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
@@ -5183,24 +5216,24 @@
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の施策目標のうち1指標が測定できない</t>
+          <t>障がい者票に介護保険・65歳到達に関する設問がない</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない</t>
+          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>発送前であれば問13の後に外出目的の設問を追加するか、問45の選択肢を前回に揃える。発送後であれば別の把握方法へ切り替える旨を村と協議する</t>
+          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳での確認に一本化する</t>
         </is>
       </c>
       <c r="G18" s="30" t="inlineStr">
@@ -5212,42 +5245,79 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="32" t="inlineStr">
         <is>
+          <t>R-11</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>第4次障がい者計画の施策目標のうち1指標が測定できない</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>発送前であれば問13の後に外出目的の設問を追加するか、問45の選択肢を前回に揃える。発送後であれば別の把握方法へ切り替える旨を村と協議する</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="inlineStr">
+        <is>
+          <t>判断待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>供給</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>圏域事業所の受入可能量が見込量の上限になる</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>村内に事業所がなく、送迎・人材・定員が制約となる</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>圏域事業所へ照会し、利用希望量と利用可能量を分けて管理する</t>
         </is>
       </c>
-      <c r="G19" s="32" t="inlineStr">
+      <c r="G20" s="30" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G19"/>
+  <autoFilter ref="A5:G20"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -5068,9 +5068,9 @@
           <t>推計</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>平均生活日数はNDB通常集計327.1日・公費含む集計323.8日、1年以上入院患者数は県計画(630調査)2,808人・NDB通常2,449人・NDB公費2,758人・ReMHRAD(630調査R7)2,220人と、出典により値が異なる。告示のCが630調査の実人数かNDBの1日平均在院患者数かも特定できていない</t>
+          <t>【一部解消】令和5年度630調査 Ⅲ.2.(11) の受領により、別表第四のCは住所地ベース2,591人（65歳未満901人・65歳以上1,690人）と確定。県第7期計画の長期在院者数と同系統であることも確認。残るのは平均生活日数のNDB通常集計327.1日と公費含む集計323.8日の使い分け</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>国の算定要領を県経由で確認する。計画本文には出典と時点を必ず併記する</t>
+          <t>計画本文には出典・時点・集計区分を必ず併記する。公費含む集計を用いるか否かは県の第8期計画に合わせる</t>
         </is>
       </c>
       <c r="G14" s="30" t="inlineStr">

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_仕様書別進捗'!$A$5:$I$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3819,7 +3819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3916,100 +3916,100 @@
       <c r="G6" s="37" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>村内3事業所の詳細</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ReMHRAD障害福祉資源で確認した居宅介護1・重度訪問介護1・生活介護1について、事業所名、指定年月、共生型サービスの指定の有無、受入可能人数、送迎範囲</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>骨子案修正版 第5章8／サービス見込量 08</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G7" s="37" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>圏域事業所の制度活用状況</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>共生型サービスの指定の有無、多機能型・従たる事業所の設置可能性、介護保険事業所（訪問介護・居宅介護支援）の居宅介護指定取得の意向</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>骨子案修正版 第5章8／サービス見込量 08</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="G7" s="37" t="n"/>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="G8" s="37" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>令和7年度末時点の1年以上長期入院者の実数</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>人数、年齢区分（65歳未満／65歳以上／75歳以上／40歳以上の認知症の別）、入院先、退院の可能性。現行計画の令和5年度5人が起点。村・会津保健所で確認</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>骨子案修正版 第4章(2)</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G8" s="37" t="n"/>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>福島県の長期入院患者に係る基盤整備量（利用者数）</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>県が基本指針 別表第四の三の項の式により算定した令和11年度末の値。県第7期計画は一・二の項に相当する長期在院者数（R8末目標 65歳未満898人・65歳以上1,656人）のみ掲載し三の項は無いため、県への個別照会が必要</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>骨子案修正版 第4章(2)</t>
-        </is>
-      </c>
-      <c r="E9" s="32" t="inlineStr">
-        <is>
-          <t>県照会中</t>
-        </is>
-      </c>
-      <c r="F9" s="26" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
         </is>
       </c>
       <c r="G9" s="37" t="n"/>
@@ -4022,93 +4022,93 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>福島県の長期入院患者に係る基盤整備量（利用者数）</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>県が基本指針 別表第四の三の項の式により算定した令和11年度末の値。県第7期計画は一・二の項に相当する長期在院者数（R8末目標 65歳未満898人・65歳以上1,656人）のみ掲載し三の項は無いため、県への個別照会が必要</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>骨子案修正版 第4章(2)</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>県照会中</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="n"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
           <t>令和6年度の一般就労移行実績・就労定着支援利用実績</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>成果目標の倍率（全体1.31倍、就労移行支援1.14倍、A型おおむね1.52倍、B型おおむね1.67倍、就労定着支援1.47倍）の基準値。事業種別ごとに必要</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>骨子案修正版 第4章(3)</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G10" s="37" t="n"/>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="G11" s="37" t="n"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>第7期計画の令和8年度目標の達成見込み</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>未達の場合、未達成割合を令和11年度目標に上乗せする規定がある（第二 一・三）。本村は地域移行0人・削減0人が目標のため、達成／未達の整理が必要</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>骨子案修正版 第4章(1)(3)</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="n"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>最優先</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>年齢別・サービス別の匿名利用者一覧</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>利用者番号、生年月、障害支援区分、利用中のサービス、月利用日数・時間。氏名不要</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>サービス見込量 02・03・04</t>
-        </is>
-      </c>
-      <c r="E12" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G12" s="37" t="n"/>
@@ -4121,17 +4121,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>サービス別の支給決定者数（実人数）</t>
+          <t>年齢別・サービス別の匿名利用者一覧</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>請求件数ではなく実人数。計画相談支援は請求と実人数が一致しないため特に必要</t>
+          <t>利用者番号、生年月、障害支援区分、利用中のサービス、月利用日数・時間。氏名不要</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 03・04</t>
+          <t>サービス見込量 02・03・04</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
@@ -4154,50 +4154,50 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>サービス別の支給決定者数（実人数）</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>請求件数ではなく実人数。計画相談支援は請求と実人数が一致しないため特に必要</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>サービス見込量 03・04</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G14" s="37" t="n"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
           <t>年齢階級別の手帳所持者数・人口</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>身体は0〜17／18〜39／40〜64／65〜74／75歳以上、療育・精神は18歳未満／18〜64／65歳以上</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>将来推計 05</t>
-        </is>
-      </c>
-      <c r="E14" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G14" s="37" t="n"/>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>令和6・7年度実績、令和8年度見込</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>成果目標、サービス別利用者数・利用量、給付費、地域生活支援事業、相談件数</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>前回計画評価／サービス見込量／財源構成案</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
@@ -4220,17 +4220,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>発送対象者数（重複除外後）</t>
+          <t>令和6・7年度実績、令和8年度見込</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>仕様書の約190人の内訳と、現行計画156人との差の理由</t>
+          <t>成果目標、サービス別利用者数・利用量、給付費、地域生活支援事業、相談件数</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>契約管理5／アンケート発送設計</t>
+          <t>前回計画評価／サービス見込量／財源構成案</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G16" s="37" t="n"/>
@@ -4253,17 +4253,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>宛名ラベルシール</t>
+          <t>発送対象者数（重複除外後）</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>仕様書Ⅰ(1)により委託者が抽出し提供</t>
+          <t>仕様書の約190人の内訳と、現行計画156人との差の理由</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>アンケート発送</t>
+          <t>契約管理5／アンケート発送設計</t>
         </is>
       </c>
       <c r="E17" s="27" t="inlineStr">
@@ -4286,17 +4286,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>特別支援学校・特別支援学級の在籍者</t>
+          <t>宛名ラベルシール</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>学年、卒業予定年度、卒業後の進路。令和6〜7年度に卒業した方の現在の利用状況も含む</t>
+          <t>仕様書Ⅰ(1)により委託者が抽出し提供</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>サービス見込量 02・03</t>
+          <t>アンケート発送</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G18" s="37" t="n"/>
@@ -4319,93 +4319,93 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
+          <t>特別支援学校・特別支援学級の在籍者</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>学年、卒業予定年度、卒業後の進路。令和6〜7年度に卒業した方の現在の利用状況も含む</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>サービス見込量 02・03</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G19" s="37" t="n"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>令和9〜11年度の65歳到達者</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>到達年度、現在利用しているサービス、月量</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>サービス見込量 02・06</t>
         </is>
       </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="G19" s="37" t="n"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="G20" s="37" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>前回調査の調査結果報告書</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>発送164人・回収95人・回収率57.9%。設問別の集計結果を収録</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>アンケート集計設計・経年比較</t>
         </is>
       </c>
-      <c r="E20" s="36" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F21" s="26" t="inlineStr">
         <is>
           <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G20" s="37" t="n"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>小規模公表基準</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>n&lt;5の秘匿、地区別・障がい種別クロスの扱い</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>アンケート集計・報告書</t>
-        </is>
-      </c>
-      <c r="E21" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-      <c r="F21" s="26" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G21" s="37" t="n"/>
@@ -4418,17 +4418,17 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉関係の歳入歳出決算</t>
+          <t>小規模公表基準</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>自立支援給付費負担金、障害児施設給付費負担金、地域生活支援事業費補助金の交付額と村負担</t>
+          <t>n&lt;5の秘匿、地区別・障がい種別クロスの扱い</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>財源構成案 04・06・07</t>
+          <t>アンケート集計・報告書</t>
         </is>
       </c>
       <c r="E22" s="27" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G22" s="37" t="n"/>
@@ -4451,60 +4451,60 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>障がい福祉関係の歳入歳出決算</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>自立支援給付費負担金、障害児施設給付費負担金、地域生活支援事業費補助金の交付額と村負担</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>財源構成案 04・06・07</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G23" s="37" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>令和6・7年度の障害児給付費の変動理由</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>児童発達支援23件→1件、放課後等デイ12件→27件の理由。受給者単位で就学移行かを確認</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>サービス見込量 04／計画本文</t>
         </is>
       </c>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G23" s="37" t="n"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>現行計画本編（第4次障がい者計画・第7期・第3期）</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>本編63頁、アンケート調査結果報告書69頁、概要版4頁。令和6年3月策定</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>全体（年齢3区分別人口・前回調査の内訳を反映済み）</t>
-        </is>
-      </c>
-      <c r="E24" s="36" t="inlineStr">
-        <is>
-          <t>受領済</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G24" s="37" t="n"/>
@@ -4512,32 +4512,32 @@
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="32" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>圏域事業所の受入可能性</t>
+          <t>現行計画本編（第4次障がい者計画・第7期・第3期）</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>定員、空き、送迎範囲、受入可否。介護保険事業所の共生型サービス指定の有無を含む</t>
+          <t>本編63頁、アンケート調査結果報告書69頁、概要版4頁。令和6年3月策定</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 08</t>
-        </is>
-      </c>
-      <c r="E25" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+          <t>全体（年齢3区分別人口・前回調査の内訳を反映済み）</t>
+        </is>
+      </c>
+      <c r="E25" s="36" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
       <c r="F25" s="26" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G25" s="37" t="n"/>
@@ -4550,17 +4550,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>医療的ケア児者・地域生活支援拠点・個別避難計画の実態</t>
+          <t>圏域事業所の受入可能性</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>対象者数、支援内容、拠点の検証会・緊急対応、名簿・計画の作成状況</t>
+          <t>定員、空き、送迎範囲、受入可否。介護保険事業所の共生型サービス指定の有無を含む</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>計画本文 第4章・第6章</t>
+          <t>サービス見込量 08</t>
         </is>
       </c>
       <c r="E26" s="27" t="inlineStr">
@@ -4583,17 +4583,17 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
+          <t>医療的ケア児者・地域生活支援拠点・個別避難計画の実態</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>関連計画との整合確認</t>
+          <t>対象者数、支援内容、拠点の検証会・緊急対応、名簿・計画の作成状況</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>計画本文 第1章・第7章</t>
+          <t>計画本文 第4章・第6章</t>
         </is>
       </c>
       <c r="E27" s="27" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>40歳以上65歳未満の特定疾病該当者</t>
+          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+          <t>関連計画との整合確認</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>サービス見込量 02</t>
+          <t>計画本文 第1章・第7章</t>
         </is>
       </c>
       <c r="E28" s="27" t="inlineStr">
@@ -4649,42 +4649,75 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
+          <t>40歳以上65歳未満の特定疾病該当者</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>サービス見込量 02</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F29" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G29" s="37" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>自立支援協議会の委員名簿</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>任期・氏名・所属・役職</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>計画書 資料編</t>
         </is>
       </c>
-      <c r="E29" s="27" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F29" s="26" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="G29" s="37" t="n"/>
-    </row>
-    <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>未受領：24件（うち最優先3件、高9件）。最優先の3件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。</t>
+      <c r="G30" s="37" t="n"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>未受領：25件（うち最優先3件、高9件）。最優先の3件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G29"/>
+  <autoFilter ref="A5:G30"/>
   <mergeCells count="3">
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -4698,7 +4731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5112,17 +5145,17 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>村内に障がい福祉サービス事業所が1か所もない</t>
+          <t>会津北部圏域の訪問系サービス事業所が本村の1か所のみになっている</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>基本指針 第三の二の2(二)は、訪問系サービス及び指定通所支援について「各市町村において事業を実施する事業所を最低一箇所確保できるよう努める」としている。本村は0か所であり、圏域及び近隣市の事業所に全面的に依存している。事業所の撤退・受入制限がそのまま利用不能につながる</t>
+          <t>ReMHRAD障害福祉資源によれば、令和7年時点で本村に居宅介護1・重度訪問介護1・生活介護1の事業所がある一方、猪苗代町の居宅介護・重度訪問介護は令和2年の各1か所から0か所へ減った。圏域4町村で訪問系サービスを提供する事業所は本村の1か所のみ。この1か所が撤退すると圏域全体が会津若松市・喜多方市への依存となる</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>告示が示す工夫（介護保険事業所への居宅介護指定の働きかけ、共生型サービスの周知、基準該当障害福祉サービス、多機能型・従たる事業所）を骨子案修正版 第5章8 に位置づけた。圏域4町村の担当者会議で各制度の活用可能性を確認する</t>
+          <t>告示が示す工夫（介護保険事業所への居宅介護指定の働きかけ、共生型サービスの周知、基準該当障害福祉サービス、多機能型・従たる事業所）を骨子案修正版 第5章8 に位置づけた。圏域4町村の担当者会議で各制度の活用可能性と訪問系の提供体制を協議する</t>
         </is>
       </c>
       <c r="G15" s="32" t="inlineStr">
@@ -5134,12 +5167,12 @@
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-16</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>財源</t>
+          <t>記述</t>
         </is>
       </c>
       <c r="C16" s="34" t="inlineStr">
@@ -5149,17 +5182,17 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>令和8年度・令和9年度の報酬改定により単価前提が動く</t>
+          <t>骨子案・当方資料の「本村には事業所がない」という記述が事実と異なる</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>令和8年6月施行の処遇改善加算拡充（月1.0万円＝3.3%＋上乗せ1.0%）とB型基本報酬区分見直し。さらに令和9年度報酬改定が見込まれ、計画期間の初年度に当たる。令和7年度実績単価を据え置くと給付費推計が実勢とずれる</t>
+          <t>ReMHRAD障害福祉資源で、令和7年時点に居宅介護1・重度訪問介護1・生活介護1の事業所を確認。令和2年時点はいずれも0か所であり、その後の指定と考えられる。骨子案原本の「就労継続支援事業所がなく」「児童発達支援センター0か所」は事実と一致</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>財源構成案 08シートに改定率パラメータを設置済み。改定内容の確定後に入力する</t>
+          <t>骨子案修正版 第5章8 を原典から表を生成する方式に変更済み。事業所名・指定年月・共生型指定の有無・受入可能人数を村に確認する</t>
         </is>
       </c>
       <c r="G16" s="30" t="inlineStr">
@@ -5171,12 +5204,12 @@
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="32" t="inlineStr">
         <is>
-          <t>R-8</t>
+          <t>R-13</t>
         </is>
       </c>
       <c r="B17" s="32" t="inlineStr">
         <is>
-          <t>品質</t>
+          <t>財源</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
@@ -5186,17 +5219,17 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>障がい児版調査票のルビ構造により本文が欠落して見える箇所がある</t>
+          <t>令和8年度・令和9年度の報酬改定により単価前提が動く</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>問1〜問15で語句が欠けて抽出される。Word表示上は正常な可能性もある</t>
+          <t>令和8年6月施行の処遇改善加算拡充（月1.0万円＝3.3%＋上乗せ1.0%）とB型基本報酬区分見直し。さらに令和9年度報酬改定が見込まれ、計画期間の初年度に当たる。令和7年度実績単価を据え置くと給付費推計が実勢とずれる</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Word上でルビなしテキストとして読んで意味が通るかを確認する</t>
+          <t>財源構成案 08シートに改定率パラメータを設置済み。改定内容の確定後に入力する</t>
         </is>
       </c>
       <c r="G17" s="32" t="inlineStr">
@@ -5208,12 +5241,12 @@
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>R-9</t>
+          <t>R-8</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>品質</t>
         </is>
       </c>
       <c r="C18" s="34" t="inlineStr">
@@ -5223,29 +5256,29 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>障がい者票に介護保険・65歳到達に関する設問がない</t>
+          <t>障がい児版調査票のルビ構造により本文が欠落して見える箇所がある</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない</t>
+          <t>問1〜問15で語句が欠けて抽出される。Word表示上は正常な可能性もある</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳での確認に一本化する</t>
+          <t>Word上でルビなしテキストとして読んで意味が通るかを確認する</t>
         </is>
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
-          <t>判断待ち</t>
+          <t>対応中</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-9</t>
         </is>
       </c>
       <c r="B19" s="32" t="inlineStr">
@@ -5253,24 +5286,24 @@
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の施策目標のうち1指標が測定できない</t>
+          <t>障がい者票に介護保険・65歳到達に関する設問がない</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない</t>
+          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>発送前であれば問13の後に外出目的の設問を追加するか、問45の選択肢を前回に揃える。発送後であれば別の把握方法へ切り替える旨を村と協議する</t>
+          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳での確認に一本化する</t>
         </is>
       </c>
       <c r="G19" s="32" t="inlineStr">
@@ -5282,42 +5315,79 @@
     <row r="20" ht="46" customHeight="1">
       <c r="A20" s="30" t="inlineStr">
         <is>
+          <t>R-11</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>第4次障がい者計画の施策目標のうち1指標が測定できない</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>発送前であれば問13の後に外出目的の設問を追加するか、問45の選択肢を前回に揃える。発送後であれば別の把握方法へ切り替える旨を村と協議する</t>
+        </is>
+      </c>
+      <c r="G20" s="30" t="inlineStr">
+        <is>
+          <t>判断待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>供給</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>圏域事業所の受入可能量が見込量の上限になる</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>村内に事業所がなく、送迎・人材・定員が制約となる</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>圏域事業所へ照会し、利用希望量と利用可能量を分けて管理する</t>
         </is>
       </c>
-      <c r="G20" s="30" t="inlineStr">
+      <c r="G21" s="32" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G20"/>
+  <autoFilter ref="A5:G21"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>人数、年齢区分（65歳未満／65歳以上／75歳以上／40歳以上の認知症の別）、入院先、退院の可能性。現行計画の令和5年度5人が起点。村・会津保健所で確認</t>
+          <t>人数、年齢区分（65歳未満／65歳以上／75歳以上／40歳以上の認知症の別）、入院先、退院の可能性。現行計画の令和5年度5人が起点。村・会津保健所で確認。ReMHRADで把握できるのは入院期間を問わない在院患者数まで（R4:7人・R5:10人・R6:8人）で、1年以上の内訳と年齢区分は公表データからは得られない</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_課題・リスク" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_打合せ記録" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_更新履歴" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_分量配分計画" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_仕様書別進捗'!$A$5:$I$38</definedName>
@@ -27,10 +28,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="+0.0;-0.0;0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,6 +72,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="15">
@@ -214,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -328,6 +336,36 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2151,16 +2189,16 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_サービス見込量.xlsx（09_地域生活支援事業）／財源構成案.xlsx（06）</t>
-        </is>
-      </c>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>村資料待ち</t>
+          <t>北塩原村_地域生活支援事業.xlsx（4シート）／骨子案修正版 第5章9「事業ごとの実施に関する考え方」</t>
+        </is>
+      </c>
+      <c r="E22" s="34" t="inlineStr">
+        <is>
+          <t>作業中</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="G22" s="30" t="inlineStr">
         <is>
@@ -2174,7 +2212,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>移動支援0人の理由（制度未周知／代替／ニーズ不在）を確認する。事業別の事業費・補助額・村負担</t>
+          <t>告示第三の二の3が定める4事項との対応を確認し、不足していた「事業ごとの実施に関する考え方」を計画本文に追加。移動支援0人の理由、福祉ホームの実績と見込の逆転、見込量表に行がない2事業（法人後見支援・手話奉仕員養成研修）の扱いを村へ確認する。事業別の事業費・補助額・村負担額も未受領</t>
         </is>
       </c>
     </row>
@@ -2196,16 +2234,16 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>骨子案 第4章（8区分＋国基準数値＋村の目標値案）</t>
-        </is>
-      </c>
-      <c r="E23" s="27" t="inlineStr">
-        <is>
-          <t>村資料待ち</t>
+          <t>骨子案修正版 第4章（成果目標8項目）・第5章10（活動指標）／北塩原村_活動指標.xlsx（4シート）</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>作業中</t>
         </is>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G23" s="32" t="inlineStr">
         <is>
@@ -2219,7 +2257,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>令和7年度末の施設入所者数等の基準値を受領する。活動指標を成果目標と区分して整理する</t>
+          <t>活動指標は骨子案に節・表がなく未着手だったが、告示別表第一の83項目から本村分65項目を抽出し、必須33（サービスの見込量に相当）と任意（第三の四㈡）を区分した上で第5章10として新設。成果目標は令和7年度末の施設入所者数等の基準値を受領するまで数値が確定しない</t>
         </is>
       </c>
     </row>
@@ -2371,21 +2409,21 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>計画策定委員会の支援（会議資料の作成、会議への出席、会議記録の作成）。協議会の開催は1回程度。</t>
+          <t>計画策定委員会の支援（会議資料の作成、会議への出席、会議記録の作成）。協議会の開催は村</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E27" s="28" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>北塩原村_協議会等資料_構成案.md（協議会9資料・庁議4資料・パブコメ資料の構成と論点）</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t>作業中</t>
         </is>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="G27" s="32" t="inlineStr">
         <is>
@@ -2399,7 +2437,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>開催日の確定。報告・説明の主体は村。受託者は資料作成・出席・記録作成</t>
+          <t>3種の会議（自立支援協議会・庁議・パブリックコメント）の資料構成と論点を整理済み。村資料に依存しない資料2（基本指針の改正点）・資料8（提供体制の課題）・資料1（策定の概要）は作成に着手できる。協議会が令和8年12月の1回のみで第8期の審議事項を賄えるか、2回への分割を村と協議する</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2504,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>骨子案修正版（30ページ相当）</t>
+          <t>骨子案修正版（本文約45頁）／分量配分計画（docs・進捗管理08）</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
@@ -2475,7 +2513,7 @@
         </is>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G29" s="32" t="inlineStr">
         <is>
@@ -2489,7 +2527,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>本文の確定後に組版。60頁の想定に対する現在の分量を確認する</t>
+          <t>現行計画63頁の章別配分を基準に、章ごとの目標頁数を設定済み（合計60頁）。現在の本文は注記を除き約45頁で15頁の余地がある。第5章に20頁を配分。第1章の原稿確定後に実組版で1頁あたりの文字数を実測し配分計画を補正する</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3197,7 +3235,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>サービス見込量の個別積上げ（11シート）</t>
+          <t>サービス見込量の個別積上げ（13シート）</t>
         </is>
       </c>
       <c r="D14" s="24" t="n"/>
@@ -3209,24 +3247,24 @@
       <c r="F14" s="24" t="n"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>年齢到達者一覧、65歳移行判定、供給制約を含む</t>
+          <t>年齢到達者一覧、65歳移行判定、供給制約、告示別表第一根拠、別表第五判定を含む</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="32" t="inlineStr">
         <is>
-          <t>財源</t>
+          <t>推計</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_財源構成案.xlsx</t>
+          <t>北塩原村_活動指標.xlsx</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>国・県・村の負担内訳（10シート）</t>
+          <t>活動指標の設定（4シート）</t>
         </is>
       </c>
       <c r="D15" s="24" t="n"/>
@@ -3238,224 +3276,315 @@
       <c r="F15" s="24" t="n"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>給付実績R2〜R7、財源構成試算、見込量×単価の積上げ</t>
+          <t>別表第一の83項目。必須33・任意。仕様書4-Ⅱ(3)⑤に対応</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>評価</t>
+          <t>資源</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>北塩原村_現行計画評価.xlsx</t>
+          <t>北塩原村_圏域サービス資源.xlsx</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>現行計画の評価（7シート）</t>
+          <t>圏域の事業所数（5シート）</t>
         </is>
       </c>
       <c r="D16" s="24" t="n"/>
-      <c r="E16" s="34" t="inlineStr">
-        <is>
-          <t>作業中</t>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="F16" s="24" t="n"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>令和3〜5年度の見込量と実績の突合、成果目標・施策目標の評価</t>
+          <t>ReMHRAD障害福祉資源18サービス×市町村別、2020→2025</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="32" t="inlineStr">
         <is>
-          <t>管理</t>
+          <t>精神</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_業務進捗管理.xlsx</t>
+          <t>福島県_精神医療指標抽出.xlsx</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>本ブック</t>
+          <t>福島県の精神医療指標（7シート）</t>
         </is>
       </c>
       <c r="D17" s="24" t="n"/>
-      <c r="E17" s="34" t="inlineStr">
-        <is>
-          <t>作業中</t>
+      <c r="E17" s="36" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="F17" s="24" t="n"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>納品対象とするか村と確認</t>
+          <t>平均生活日数・再入院率・長期入院患者・別表第四の当てはめ・村の在院者</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>調査</t>
+          <t>財源</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>0728北塩原村_障がい福祉アンケート調査票.docx</t>
+          <t>北塩原村_財源構成案.xlsx</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>調査票（障がい者版・52問）</t>
+          <t>国・県・村の負担内訳（10シート）</t>
         </is>
       </c>
       <c r="D18" s="24" t="n"/>
-      <c r="E18" s="33" t="inlineStr">
-        <is>
-          <t>概ね完了</t>
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>作業中</t>
         </is>
       </c>
       <c r="F18" s="24" t="n"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>最終目視確認が残</t>
+          <t>給付実績R2〜R7、財源構成試算、見込量×単価の積上げ</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>調査</t>
+          <t>評価</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>0728北塩原村_障がい児福祉アンケート調査票.docx</t>
+          <t>北塩原村_現行計画評価.xlsx</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>調査票（障がい児版・51問）</t>
+          <t>現行計画の評価（7シート）</t>
         </is>
       </c>
       <c r="D19" s="24" t="n"/>
-      <c r="E19" s="33" t="inlineStr">
-        <is>
-          <t>概ね完了</t>
+      <c r="E19" s="34" t="inlineStr">
+        <is>
+          <t>作業中</t>
         </is>
       </c>
       <c r="F19" s="24" t="n"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>ルビ構造の確認が残</t>
+          <t>令和3〜5年度の見込量と実績の突合、成果目標・施策目標の評価</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>調査</t>
+          <t>管理</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Googleフォーム自動作成 Code（.gs）</t>
+          <t>北塩原村_業務進捗管理.xlsx</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>ウェブ回答フォームの生成スクリプト</t>
+          <t>本ブック</t>
         </is>
       </c>
       <c r="D20" s="24" t="n"/>
-      <c r="E20" s="33" t="inlineStr">
-        <is>
-          <t>概ね完了</t>
+      <c r="E20" s="34" t="inlineStr">
+        <is>
+          <t>作業中</t>
         </is>
       </c>
       <c r="F20" s="24" t="n"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>選択肢順序の固定が残</t>
+          <t>納品対象とするか村と確認</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>調査</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_障がいサービス給付実績_整理版.xlsx</t>
+          <t>0728北塩原村_障がい福祉アンケート調査票.docx</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>受領データの整理版（6シート）</t>
+          <t>調査票（障がい者版・52問）</t>
         </is>
       </c>
       <c r="D21" s="24" t="n"/>
-      <c r="E21" s="36" t="inlineStr">
-        <is>
-          <t>完了</t>
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>概ね完了</t>
         </is>
       </c>
       <c r="F21" s="24" t="n"/>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>令和2〜7年度、介護給付費・障害児給付費</t>
+          <t>最終目視確認が残</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="30" t="inlineStr">
         <is>
-          <t>報告</t>
+          <t>調査</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>調査結果報告書（未作成）</t>
+          <t>0728北塩原村_障がい児福祉アンケート調査票.docx</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>アンケート集計結果</t>
+          <t>調査票（障がい児版・51問）</t>
         </is>
       </c>
       <c r="D22" s="24" t="n"/>
-      <c r="E22" s="28" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>概ね完了</t>
         </is>
       </c>
       <c r="F22" s="24" t="n"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
+          <t>ルビ構造の確認が残</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>調査</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Googleフォーム自動作成 Code（.gs）</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>ウェブ回答フォームの生成スクリプト</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>概ね完了</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>選択肢順序の固定が残</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>北塩原村_障がいサービス給付実績_整理版.xlsx</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>受領データの整理版（6シート）</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="36" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>令和2〜7年度、介護給付費・障害児給付費</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>報告</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>調査結果報告書（未作成）</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>アンケート集計結果</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
           <t>集計後</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="31">
     <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E23:F23"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
@@ -3464,7 +3593,9 @@
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E22:F22"/>
@@ -5916,4 +6047,512 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>計画書の分量配分計画（成果品①：A4判・両面約60頁）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>村資料が揃ってから分量を考えると組版段階で削る作業が発生するため、章ごとの目標頁数を先に決める。現在の本文頁は骨子案修正版の実測（作業用の注記を除く。本文1,100字／頁、表0.15頁、図0.35頁で概算）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>章</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>現行計画
+（63頁）</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>現在の
+本文頁</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>目標頁</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>増減</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>第1章 計画の策定にあたって</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D6" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>基本指針の改正16項目が中心。現行9頁には基本理念・体系（第3章へ移動）が含まれる</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>第2章 本村の障がい者の現状</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>手帳所持者数の将来推計（仕様書4-Ⅱ(3)①）を新設したため現行より増</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>第3章 基本理念・基本目標及び施策体系</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" s="41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D8" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>改定対象外の第4次障がい者計画の再掲。骨格と第8期で加わる視点との対応表に絞る</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>第4章 令和11年度に向けた成果目標</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" s="44" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="45" t="n">
+        <v>1.699999999999999</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>7項目→8項目。目標値・考え方の記入で増える</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>第5章 サービス等の実績と今後の見込み量</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" s="41" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="D10" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="42" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>推計方法・年齢到達移行・活動指標・財源構成を新設。本計画の実質的な付加価値</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>第6章 成年後見制度の利用促進</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>現行と同水準。中核機関の記述を補う</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>第7章 他計画との連携</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D12" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>新設章。健康21・こども子育て計画等</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>第8章 資料編</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D13" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>アンケート集計結果は成果品②（別冊約60頁）に収め、計画書は要約と委員名簿のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="46" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B14" s="47">
+        <f>SUM(B6:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="47">
+        <f>ROUND(SUM(C6:C13),0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="47">
+        <f>SUM(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="48">
+        <f>D14-C14</f>
+        <v/>
+      </c>
+      <c r="F14" s="46" t="inlineStr">
+        <is>
+          <t>目標60頁。現在の本文約45頁に対し15頁の余地がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>60頁に収まらない場合の削減順序（上から削る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>削減対象</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>第3章の施策別の記述</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>改定対象外の再掲であり、詳細は第4次障がい者計画本体を参照すればよい</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>第1章の基本指針改正16項目</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>16項目すべてを列挙せず、本村に関係する項目に絞る</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>第8章の資料編</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>成果品②へ移す</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>第5章の実績値の年次</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>令和2年度からの6年分を令和5年度からの4年分に短縮する</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>削ってはならないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>第4章の成果目標8項目</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>基本指針が求める必須事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>第5章のサービス見込量</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>別表第二 三の項の必須記載事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>第5章の活動指標のうち見込量に相当するもの</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>同上（第三 四㈡により見込量以外は任意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>第5章1の推計方法</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>別表第五の適用判定を含む算定根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>※ 本頁換算は文字数からの概算であり、実際の頁数はスタイル（フォントサイズ・行間・余白）で変わる。第1章の原稿が固まった時点で実際の組版にかけ、1頁あたりの文字数を実測して本計画を補正する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_将来推計.xlsx（03_手帳将来推計・04_推計の不確実性・05_年齢階級別推計）／骨子案修正版 第2章6</t>
+          <t>北塩原村_将来推計.xlsx（9シート。08_県との比較を追加）／骨子案修正版 第2章6</t>
         </is>
       </c>
       <c r="E19" s="27" t="inlineStr">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="G19" s="32" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>現行計画本編の受領により年齢3区分別人口5年分が判明し、所持率の推移を算定できた。令和6〜8年度実績と年齢階級別内訳を受領し、方法C（年齢階級別所持率法）へ切り替える</t>
+          <t>現行計画本編の受領により年齢3区分別人口5年分が判明し、所持率の推移を算定できた。630調査により福島県の精神手帳所持者数の推移（令和5年度18,002人→令和7年度19,107人）を把握し、方法B（所持率一定）が精神で成り立たないことの傍証を得た。県の交付件数の年齢構成を村に当てはめる代替推計は、交付件数が新規交付のみで所持者の年齢構成と異なるため採用しない。方法Cには引き続き村の年齢階級別所持者数が必要</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_協議会等資料_構成案.md（協議会9資料・庁議4資料・パブコメ資料の構成と論点）</t>
+          <t>output/会議資料/（協議会資料1・2・8、庁議資料2・4の5点を作成済み）／北塩原村_協議会等資料_構成案.md（協議会9資料・庁議4資料・パブコメ資料の構成と論点）</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="G27" s="32" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>3種の会議（自立支援協議会・庁議・パブリックコメント）の資料構成と論点を整理済み。村資料に依存しない資料2（基本指針の改正点）・資料8（提供体制の課題）・資料1（策定の概要）は作成に着手できる。協議会が令和8年12月の1回のみで第8期の審議事項を賄えるか、2回への分割を村と協議する</t>
+          <t>村資料に依存しない5資料を作成済み。残る資料3〜7・9は村資料の受領後に作成する。協議会が令和8年12月の1回のみで第8期の審議事項を賄えるか、2回への分割を村と協議する。開催日の確定後、会議記録の様式（「計画への反映」欄を設ける案）を村と合意する</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3544,34 +3544,121 @@
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="32" t="inlineStr">
         <is>
-          <t>報告</t>
+          <t>指標</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>調査結果報告書（未作成）</t>
+          <t>北塩原村_活動指標.xlsx</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>アンケート集計結果</t>
+          <t>活動指標の設定（4シート）</t>
         </is>
       </c>
       <c r="D25" s="24" t="n"/>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>作業中</t>
         </is>
       </c>
       <c r="F25" s="24" t="n"/>
       <c r="G25" s="7" t="inlineStr">
         <is>
+          <t>別表第一83項目。必須33・任意。仕様書4-Ⅱ(3)⑤</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>事業</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>北塩原村_地域生活支援事業.xlsx</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>地域生活支援事業（4シート）</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="34" t="inlineStr">
+        <is>
+          <t>作業中</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>必須15・任意3。告示第三の二の3の4事項との対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>会議資料/（5ファイル）</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>協議会資料1・2・8、庁議資料2・4</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t>作業中</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>村資料に依存しない資料。残りは村資料の受領後</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>報告</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>調査結果報告書（未作成）</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>アンケート集計結果</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
           <t>集計後</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="37">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C15:D15"/>
@@ -3580,23 +3667,29 @@
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E28:F28"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C28:D28"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -19,8 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_仕様書別進捗'!$A$5:$I$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -133,17 +133,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="002CA02C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FF7F0E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002CA02C"/>
       </patternFill>
     </fill>
     <fill>
@@ -224,7 +224,7 @@
   </cellStyleXfs>
   <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -251,19 +251,19 @@
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -325,7 +325,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -355,16 +355,16 @@
     <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>0728北塩原村_障がい福祉アンケート調査票（52問）／同 障がい児福祉（51問）／0728アンケート調査票レビュー結果</t>
+          <t>0728北塩原村_障がい福祉アンケート調査票（52問）／同 障がい児福祉（51問）／0728アンケート調査票レビュー結果／村朱書き修正指示（令和8年8月・40か所）／北塩原村_アンケート調査票_村修正指示_確認結果</t>
         </is>
       </c>
       <c r="E7" s="33" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>障がい児版のルビ構造による本文欠落リスク（問1〜15）をWord上で目視確認する</t>
+          <t>村から朱書き修正指示40か所（障がい者版21・障がい児版19）を受領し内容を確認済み。修正の反映は調査票担当。当方からは問36（就労選択支援）の削除について再考を依頼中。障がい児版 問11の選択肢番号13の重複、問10の番号3の欠番も申し送り</t>
         </is>
       </c>
     </row>
@@ -2864,16 +2864,16 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>骨子案修正版に確認注記を追加済</t>
-        </is>
-      </c>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>村資料待ち</t>
+          <t>骨子案修正版の奥付を「保健福祉課福祉係」に確定</t>
+        </is>
+      </c>
+      <c r="E37" s="36" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="F37" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G37" s="32" t="inlineStr">
         <is>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="H37" s="26" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>組織改編の有無を含め村に確認する</t>
+          <t>令和8年8月の調査票修正指示で、問合せ先が「医療福祉班」から「保健福祉課 福祉係」に修正されたことにより確定。現行計画が障がい者相談支援事業の実施主体を住民課としている記載は組織改編前のものとして整理する</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3631,34 +3631,63 @@
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="30" t="inlineStr">
         <is>
-          <t>報告</t>
+          <t>村データ</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>調査結果報告書（未作成）</t>
+          <t>北塩原村_村提供実績データ.xlsx</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>アンケート集計結果</t>
+          <t>調査票の朱書きで判明した村の実データ（7シート）</t>
         </is>
       </c>
       <c r="D28" s="24" t="n"/>
-      <c r="E28" s="28" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="E28" s="36" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="F28" s="24" t="n"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
+          <t>実データ9件・修正指示40か所・照会事項8件。骨子案 第4章(3)(4)(6)・第5章1へ反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>報告</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>調査結果報告書（未作成）</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>アンケート集計結果</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
           <t>集計後</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="39">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C15:D15"/>
@@ -3671,7 +3700,9 @@
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C29:D29"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E29:F29"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="E28:F28"/>
@@ -4043,7 +4074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4259,7 +4290,7 @@
           <t>骨子案修正版 第4章(2)</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>県照会中</t>
         </is>
@@ -4812,17 +4843,17 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>対象者数、支援内容、拠点の検証会・緊急対応、名簿・計画の作成状況</t>
+          <t>【一部受領】令和8年8月の調査票朱書きで、医療的ケア児1人（経管栄養が毎日必要）、個別避難計画の作成0件を確認。なお必要なのは、医療的ケア児1人の年齢・就学状況、拠点の検証会・緊急対応の実績、避難行動要支援者名簿の登載者数</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>計画本文 第4章・第6章</t>
-        </is>
-      </c>
-      <c r="E27" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+          <t>計画本文 第4章・第6章／村提供実績データ 01</t>
+        </is>
+      </c>
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>一部受領</t>
         </is>
       </c>
       <c r="F27" s="26" t="inlineStr">
@@ -4833,34 +4864,34 @@
       <c r="G27" s="37" t="n"/>
     </row>
     <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>最優先</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
+          <t>障害支援区分別人数の基準日とサービス利用状況</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>関連計画との整合確認</t>
+          <t>【一部受領】令和8年8月の調査票朱書きで、区分2=5人・区分3=2人・区分4=5人・区分5=1人・区分6=2人（計15人、区分1は0人）を確認。基準日が示されていないため要確認。あわせて15人それぞれのサービス利用状況、区分6の2人の行動関連項目の点数、共同生活援助8人のうち区分認定を受けている者の数</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>計画本文 第1章・第7章</t>
-        </is>
-      </c>
-      <c r="E28" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+          <t>村提供実績データ 02／骨子案修正版 第5章1</t>
+        </is>
+      </c>
+      <c r="E28" s="33" t="inlineStr">
+        <is>
+          <t>一部受領</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G28" s="37" t="n"/>
@@ -4868,32 +4899,32 @@
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="32" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>40歳以上65歳未満の特定疾病該当者</t>
+          <t>セルフプラン率・基幹相談支援センター・就労選択支援事業所の状況</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+          <t>【受領済み】令和8年8月の調査票朱書きで、セルフプラン率0％、基幹相談支援センター未設置、会津管内に就労選択支援事業所なしを確認。なお必要なのは、基幹相談支援センターの第8期期間中の設置意向と4町村での検討状況、就労選択支援の圏域での協議状況</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 02</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+          <t>村提供実績データ 01／骨子案修正版 第4章(3)(6)</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t>一部受領</t>
         </is>
       </c>
       <c r="F29" s="26" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G29" s="37" t="n"/>
@@ -4901,47 +4932,179 @@
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="30" t="inlineStr">
         <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>障がい児の入所・申請の状況</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>【受領済み】令和8年8月の調査票朱書きで、障がい児入所施設・児童福祉施設の利用児0件、障害児通所支援の申請中0件を確認。第5章の障害児入所支援の見込量を0とする根拠</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>村提供実績データ 01／骨子案修正版 第4章(4)</t>
+        </is>
+      </c>
+      <c r="E30" s="36" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G30" s="37" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>アンケート調査票への村の修正指示</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>【受領済み】障がい者版17頁・障がい児版19頁のスキャンPDF。朱書き40か所。設問の削除・追加・順序変更のほか、削除理由として村の実データ9件が書き添えられている</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>村提供実績データ 05／北塩原村_アンケート調査票_村修正指示_確認結果</t>
+        </is>
+      </c>
+      <c r="E31" s="36" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+      <c r="F31" s="26" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G31" s="37" t="n"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>関連計画との整合確認</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>計画本文 第1章・第7章</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G32" s="37" t="n"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>40歳以上65歳未満の特定疾病該当者</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>サービス見込量 02</t>
+        </is>
+      </c>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F33" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G33" s="37" t="n"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>自立支援協議会の委員名簿</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>任期・氏名・所属・役職</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>計画書 資料編</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="G30" s="37" t="n"/>
-    </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>未受領：25件（うち最優先3件、高9件）。最優先の3件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。</t>
+      <c r="G34" s="37" t="n"/>
+    </row>
+    <row r="36" ht="46" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>未受領：20件（うち最優先5件、高10件）、一部受領：3件。未受領の最優先案件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。「一部受領」は令和8年8月の調査票朱書きで数値の一部が判明したもので、基準日や内訳の確認が残っています（村提供実績データ 06 参照）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G30"/>
+  <autoFilter ref="A5:G34"/>
   <mergeCells count="3">
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -4955,7 +5118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5610,8 +5773,119 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>R-17</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>就労選択支援の設問（障がい者版 問36）が削除されると、圏域確保の根拠が窓口相談実績に限られる</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>村は「会津管内に事業所がないため設問不要」と判断。しかし基本指針は令和11年度末までに各市町村又は各圏域に1事業所以上の設置を目指すとしており（全国目標は令和11年度に年間82,000人）、事業所がないことは計画に書くべき課題である。選択肢6「制度を知らない」は認知度そのもののデータで、事業所の有無とは独立して意味がある</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>村に再考を依頼済み。削除する場合でも、第5章の確保方策に「圏域内に事業所がないため会津若松地方の広域調整により確保を図る」旨を記載する（骨子案修正版 第4章(3)に反映済み）</t>
+        </is>
+      </c>
+      <c r="G22" s="30" t="inlineStr">
+        <is>
+          <t>判断待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>R-18</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>整合</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>個別避難計画0件が第4次障がい者計画の指標と矛盾する可能性がある</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>第4次障がい者計画は「個別避難計画作成 現状1件→令和11年度10件」を指標としているが、令和8年8月の村の朱書きは「作成者なし」としている。計画策定時の1件がその後失効したのか、集計方法が異なるのかが不明</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>村に確認する。第4次障がい者計画は改定対象外だが、第8期計画の第3章5（目標値と進捗管理）で現状値を示す際に整合が必要</t>
+        </is>
+      </c>
+      <c r="G23" s="32" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>R-19</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>障がい児版の設問番号に誤りがある</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>問11の選択肢番号「13」が2つある（「自傷、他害、強いこだわり、パニックなどへの対応」と「特にない」）。問10の選択肢番号は「3」が欠番。いずれも村の朱書きとは別に、通読して気づいたもの</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>調査票担当へ申し送り済み。印刷前に番号を振り直す。問10は問8との統合指示があるため、統合時に整理する</t>
+        </is>
+      </c>
+      <c r="G24" s="30" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:G21"/>
+  <autoFilter ref="A5:G24"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -19,8 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_仕様書別進捗'!$A$5:$I$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4074,7 +4074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4970,17 +4970,17 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>アンケート調査票への村の修正指示</t>
+          <t>実態調査及びPDCAサイクルに関するマニュアル（令和8年8月）</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>【受領済み】障がい者版17頁・障がい児版19頁のスキャンPDF。朱書き40か所。設問の削除・追加・順序変更のほか、削除理由として村の実データ9件が書き添えられている</t>
+          <t>【受領済み】福島県通知（8生福第2646号・8こ第2041号 令和8年8月24日）により受領。厚労省・こども家庭庁の令和8年8月19日事務連絡の別添。全81頁。令和2年版を基本指針の改正を踏まえて修正したもの</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>村提供実績データ 05／北塩原村_アンケート調査票_村修正指示_確認結果</t>
+          <t>サービス見込量 12_別表第五判定／骨子案修正版 第1章6・第5章1／北塩原村_実態調査PDCAマニュアル_確認結果</t>
         </is>
       </c>
       <c r="E31" s="36" t="inlineStr">
@@ -4990,30 +4990,30 @@
       </c>
       <c r="F31" s="26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G31" s="37" t="n"/>
     </row>
     <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
+          <t>PDCAの評価体制・スケジュール・公表方法</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>関連計画との整合確認</t>
+          <t>自立支援協議会と庁内会議体の役割分担、実績把握と評価の時期（村の予算編成に合わせる）、中間評価の結果の公表方法（ホームページ・広報誌・協議会資料の公開範囲）</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>計画本文 第1章・第7章</t>
+          <t>骨子案修正版 第1章6</t>
         </is>
       </c>
       <c r="E32" s="27" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="G32" s="37" t="n"/>
@@ -5031,32 +5031,32 @@
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="32" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>40歳以上65歳未満の特定疾病該当者</t>
+          <t>アンケート調査票への村の修正指示</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+          <t>【受領済み】障がい者版17頁・障がい児版19頁のスキャンPDF。朱書き40か所。設問の削除・追加・順序変更のほか、削除理由として村の実データ9件が書き添えられている</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 02</t>
-        </is>
-      </c>
-      <c r="E33" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+          <t>村提供実績データ 05／北塩原村_アンケート調査票_村修正指示_確認結果</t>
+        </is>
+      </c>
+      <c r="E33" s="36" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
       <c r="F33" s="26" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G33" s="37" t="n"/>
@@ -5069,42 +5069,108 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
+          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>関連計画との整合確認</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>計画本文 第1章・第7章</t>
+        </is>
+      </c>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G34" s="37" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>40歳以上65歳未満の特定疾病該当者</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>サービス見込量 02</t>
+        </is>
+      </c>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G35" s="37" t="n"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>自立支援協議会の委員名簿</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>任期・氏名・所属・役職</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>計画書 資料編</t>
         </is>
       </c>
-      <c r="E34" s="27" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="G34" s="37" t="n"/>
-    </row>
-    <row r="36" ht="46" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>未受領：20件（うち最優先5件、高10件）、一部受領：3件。未受領の最優先案件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。「一部受領」は令和8年8月の調査票朱書きで数値の一部が判明したもので、基準日や内訳の確認が残っています（村提供実績データ 06 参照）。</t>
+      <c r="G36" s="37" t="n"/>
+    </row>
+    <row r="38" ht="46" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>未受領：21件（うち最優先5件、高11件）、一部受領：3件。未受領の最優先案件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。「一部受領」は令和8年8月の調査票朱書きで数値の一部が判明したもので、基準日や内訳の確認が残っています（村提供実績データ 06 参照）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G34"/>
+  <autoFilter ref="A5:G36"/>
   <mergeCells count="3">
-    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -5118,7 +5184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5673,24 +5739,24 @@
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>障がい者票に介護保険・65歳到達に関する設問がない</t>
+          <t>障がい者票に介護保険・65歳到達に関する設問がない（国の標準項目）</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない</t>
+          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない。令和8年8月のマニュアルの調査票ひな型は問37（介護保険の利用）・問38（要介護度）・問39（利用している介護保険サービス）の3問を標準項目として置いている。同マニュアルは身体障害者の73%が65歳以上であることを踏まえ、18歳未満／18〜64歳／65歳以上の年齢階層別に分析する例を示している</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳での確認に一本化する</t>
+          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳と介護保険の認定情報の突合に一本化する</t>
         </is>
       </c>
       <c r="G19" s="32" t="inlineStr">
@@ -5717,12 +5783,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の施策目標のうち1指標が測定できない</t>
+          <t>外出目的の設問がなく、第4次障がい者計画の1指標が測定できない（国の標準項目）</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない</t>
+          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない。令和8年8月のマニュアルは図表6で「外出の目的」を主な調査項目に掲げ、「外出支援のために必要となる施策等の検討に利用」するとしている（調査票ひな型では問26）。移動支援・同行援護の見込量根拠にも直結する</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -5850,42 +5916,116 @@
     <row r="24" ht="46" customHeight="1">
       <c r="A24" s="30" t="inlineStr">
         <is>
+          <t>R-20</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>強度行動障害の該当有無を聞く設問がなく、支援ニーズの母数が特定できない</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>調査票は問20で「強度行動障がい支援に関して必要だと思う支援」を聞くが、回答者本人が該当するかを聞いていない。令和8年8月のマニュアルの調査票ひな型は問16で「強度行動障害があると言われたことはありますか」を置き、重度障害者の支援ニーズを把握するクロス集計を示している。第8期基本指針は強度行動障害を有する者の支援ニーズ把握を新規の視点としている</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>発送前であれば設問を追加する。追加しない場合は、村の朱書きで判明した区分6の2人について行動関連項目の点数を確認する（既に照会中）</t>
+        </is>
+      </c>
+      <c r="G24" s="30" t="inlineStr">
+        <is>
+          <t>判断待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>R-21</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>障害支援区分の削除は国の標準項目を落とすことになる</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>村は問7の削除を指示し、当方は対象者15人という規模から削除に異議なしと回答した。一方、令和8年8月のマニュアルは障害支援区分をクロス集計の項目として明示し（P.12）、調査票ひな型でも問35に置いている。ただし同マニュアル自身が、調査対象者数が少ない場合は標本誤差が大きくなるため集計結果の解釈を慎重に行う必要があるとしている</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>国の標準項目である旨を村へ伝えたうえで最終判断をいただく。当方の見解は変わらず、削除でも支障はない（区分別人数は役場データで把握済み）</t>
+        </is>
+      </c>
+      <c r="G25" s="32" t="inlineStr">
+        <is>
+          <t>判断待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
           <t>R-19</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C24" s="30" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>障がい児版の設問番号に誤りがある</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>問11の選択肢番号「13」が2つある（「自傷、他害、強いこだわり、パニックなどへの対応」と「特にない」）。問10の選択肢番号は「3」が欠番。いずれも村の朱書きとは別に、通読して気づいたもの</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>調査票担当へ申し送り済み。印刷前に番号を振り直す。問10は問8との統合指示があるため、統合時に整理する</t>
         </is>
       </c>
-      <c r="G24" s="30" t="inlineStr">
+      <c r="G26" s="30" t="inlineStr">
         <is>
           <t>対応中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G24"/>
+  <autoFilter ref="A5:G26"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/output/北塩原村_業務進捗管理.xlsx
+++ b/output/北塩原村_業務進捗管理.xlsx
@@ -19,8 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_仕様書別進捗'!$A$5:$I$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_村資料受領状況'!$A$5:$G$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_課題・リスク'!$A$5:$G$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -108,6 +108,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="002CA02C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
@@ -129,11 +134,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002CA02C"/>
       </patternFill>
     </fill>
     <fill>
@@ -263,22 +263,22 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -292,16 +292,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -319,13 +319,13 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1514,16 +1514,16 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>0728北塩原村_障がい福祉アンケート調査票（52問）／同 障がい児福祉（51問）／0728アンケート調査票レビュー結果／村朱書き修正指示（令和8年8月・40か所）／北塩原村_アンケート調査票_村修正指示_確認結果</t>
+          <t>0825確定版（障がい者版45問・障がい児版44問）／村朱書き修正指示40か所／北塩原村_アンケート調査票_村修正指示_確認結果</t>
         </is>
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
-          <t>概ね完了</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="F7" s="9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G7" s="32" t="inlineStr">
         <is>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>村から朱書き修正指示40か所（障がい者版21・障がい児版19）を受領し内容を確認済み。修正の反映は調査票担当。当方からは問36（就労選択支援）の削除について再考を依頼中。障がい児版 問11の選択肢番号13の重複、問10の番号3の欠番も申し送り</t>
+          <t>令和8年8月25日版で確定。村の修正指示40か所は反映済み。確定後に国のマニュアル（8月19日事務連絡・県通知8月24日）が発出されたため、標準項目3件（外出の目的・介護保険・強度行動障害の該当有無）と障害支援区分が確定版にない。クロス集計と行政データで代替する（北塩原村_クロス集計設計.xlsx）</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
           <t>14pt程度・ルビ付与・白黒印刷・専門用語への短い解説（7/7打合せで決定）</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>概ね完了</t>
         </is>
@@ -1607,7 +1607,7 @@
           <t>Googleフォーム自動作成 Code（1本統合分岐版・修正版）／設問精査レポート／修正対応メモ</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>概ね完了</t>
         </is>
@@ -1697,7 +1697,7 @@
           <t>管理番号設計（04_紙Web設計確認）</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -1874,16 +1874,16 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>北塩原村_アンケート集計分析方法_少数母数対応_計画接続メモ</t>
-        </is>
-      </c>
-      <c r="E15" s="34" t="inlineStr">
+          <t>北塩原村_アンケート集計分析方法_少数母数対応_計画接続メモ／北塩原村_クロス集計設計.xlsx（25件・層6区分・行政データ突合6件）</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
       </c>
       <c r="F15" s="9" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="G15" s="32" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
           <t>骨子案 第1章4（基本指針改正16項目、法定雇用率2.7%）／年齢到達による給付移行 調査報告／現行計画本編 第4章1（第7期の基本指針見直し）／国基準数値 原典照合結果／告示本文・新旧対照表・改正後概要（source/基本指針）／令和8年度報酬改定資料（source/報酬改定）</t>
         </is>
       </c>
-      <c r="E17" s="33" t="inlineStr">
+      <c r="E17" s="34" t="inlineStr">
         <is>
           <t>概ね完了</t>
         </is>
@@ -2012,7 +2012,7 @@
           <t>北塩原村_現行計画評価.xlsx（7シート）／前回計画評価_アンケート精査管理表／現行計画本編</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -2192,7 +2192,7 @@
           <t>北塩原村_地域生活支援事業.xlsx（4シート）／骨子案修正版 第5章9「事業ごとの実施に関する考え方」</t>
         </is>
       </c>
-      <c r="E22" s="34" t="inlineStr">
+      <c r="E22" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -2237,7 +2237,7 @@
           <t>骨子案修正版 第4章（成果目標8項目）・第5章10（活動指標）／北塩原村_活動指標.xlsx（4シート）</t>
         </is>
       </c>
-      <c r="E23" s="34" t="inlineStr">
+      <c r="E23" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -2282,7 +2282,7 @@
           <t>骨子案修正版 第3章（再構成済み）／北塩原村_現行計画評価.xlsx（03・06）</t>
         </is>
       </c>
-      <c r="E24" s="33" t="inlineStr">
+      <c r="E24" s="34" t="inlineStr">
         <is>
           <t>概ね完了</t>
         </is>
@@ -2327,7 +2327,7 @@
           <t>骨子案修正版（全8章。第2章6・第3章・第5章1・2・11を新設又は再構成）</t>
         </is>
       </c>
-      <c r="E25" s="34" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -2417,7 +2417,7 @@
           <t>output/会議資料/（協議会資料1・2・8、庁議資料2・4の5点を作成済み）／北塩原村_協議会等資料_構成案.md（協議会9資料・庁議4資料・パブコメ資料の構成と論点）</t>
         </is>
       </c>
-      <c r="E27" s="34" t="inlineStr">
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -2462,7 +2462,7 @@
           <t>令和8年7月7日 打合せ（村役場）実施済／議事録作成済</t>
         </is>
       </c>
-      <c r="E28" s="35" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>継続実施</t>
         </is>
@@ -2507,7 +2507,7 @@
           <t>骨子案修正版（本文約45頁）／分量配分計画（docs・進捗管理08）</t>
         </is>
       </c>
-      <c r="E29" s="34" t="inlineStr">
+      <c r="E29" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -2597,7 +2597,7 @@
           <t>管理ブック4本（将来推計・サービス見込量・財源構成案・業務進捗管理）</t>
         </is>
       </c>
-      <c r="E31" s="34" t="inlineStr">
+      <c r="E31" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -2732,7 +2732,7 @@
           <t>7/7議事録に記載済</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
+      <c r="E34" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -2867,7 +2867,7 @@
           <t>骨子案修正版の奥付を「保健福祉課福祉係」に確定</t>
         </is>
       </c>
-      <c r="E37" s="36" t="inlineStr">
+      <c r="E37" s="33" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -2912,7 +2912,7 @@
           <t>仕様書6。個人情報を含む資料は内部管理とし、公表用報告書と分離</t>
         </is>
       </c>
-      <c r="E38" s="35" t="inlineStr">
+      <c r="E38" s="36" t="inlineStr">
         <is>
           <t>継続実施</t>
         </is>
@@ -3044,7 +3044,7 @@
           <t>30部</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3114,7 +3114,7 @@
           <t>一式</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="D12" s="24" t="n"/>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="D13" s="24" t="n"/>
-      <c r="E13" s="34" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="D14" s="24" t="n"/>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="D15" s="24" t="n"/>
-      <c r="E15" s="34" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="D16" s="24" t="n"/>
-      <c r="E16" s="36" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="D17" s="24" t="n"/>
-      <c r="E17" s="36" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="D18" s="24" t="n"/>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="D19" s="24" t="n"/>
-      <c r="E19" s="34" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="D20" s="24" t="n"/>
-      <c r="E20" s="34" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="D21" s="24" t="n"/>
-      <c r="E21" s="33" t="inlineStr">
+      <c r="E21" s="34" t="inlineStr">
         <is>
           <t>概ね完了</t>
         </is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="D22" s="24" t="n"/>
-      <c r="E22" s="33" t="inlineStr">
+      <c r="E22" s="34" t="inlineStr">
         <is>
           <t>概ね完了</t>
         </is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="D23" s="24" t="n"/>
-      <c r="E23" s="33" t="inlineStr">
+      <c r="E23" s="34" t="inlineStr">
         <is>
           <t>概ね完了</t>
         </is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="D24" s="24" t="n"/>
-      <c r="E24" s="36" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="D25" s="24" t="n"/>
-      <c r="E25" s="34" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="D26" s="24" t="n"/>
-      <c r="E26" s="34" t="inlineStr">
+      <c r="E26" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="D27" s="24" t="n"/>
-      <c r="E27" s="34" t="inlineStr">
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="D28" s="24" t="n"/>
-      <c r="E28" s="36" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -3816,7 +3816,7 @@
           <t>当社／北塩原村</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3912,7 +3912,7 @@
           <t>当社／北塩原村</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -3944,7 +3944,7 @@
           <t>当社</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
@@ -4074,7 +4074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4158,7 +4158,7 @@
           <t>サービス見込量 12_別表第五判定</t>
         </is>
       </c>
-      <c r="E6" s="36" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
@@ -4204,7 +4204,7 @@
       <c r="G7" s="37" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4270,7 +4270,7 @@
       <c r="G9" s="37" t="n"/>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4290,7 +4290,7 @@
           <t>骨子案修正版 第4章(2)</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>県照会中</t>
         </is>
@@ -4303,7 +4303,7 @@
       <c r="G10" s="37" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4468,7 +4468,7 @@
       <c r="G15" s="37" t="n"/>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4501,7 +4501,7 @@
       <c r="G16" s="37" t="n"/>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4534,7 +4534,7 @@
       <c r="G17" s="37" t="n"/>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4567,7 +4567,7 @@
       <c r="G18" s="37" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4600,7 +4600,7 @@
       <c r="G19" s="37" t="n"/>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4653,7 +4653,7 @@
           <t>アンケート集計設計・経年比較</t>
         </is>
       </c>
-      <c r="E21" s="36" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
@@ -4666,7 +4666,7 @@
       <c r="G21" s="37" t="n"/>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4699,7 +4699,7 @@
       <c r="G22" s="37" t="n"/>
     </row>
     <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4732,7 +4732,7 @@
       <c r="G23" s="37" t="n"/>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4785,7 +4785,7 @@
           <t>全体（年齢3区分別人口・前回調査の内訳を反映済み）</t>
         </is>
       </c>
-      <c r="E25" s="36" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
@@ -4851,7 +4851,7 @@
           <t>計画本文 第4章・第6章／村提供実績データ 01</t>
         </is>
       </c>
-      <c r="E27" s="33" t="inlineStr">
+      <c r="E27" s="34" t="inlineStr">
         <is>
           <t>一部受領</t>
         </is>
@@ -4884,7 +4884,7 @@
           <t>村提供実績データ 02／骨子案修正版 第5章1</t>
         </is>
       </c>
-      <c r="E28" s="33" t="inlineStr">
+      <c r="E28" s="34" t="inlineStr">
         <is>
           <t>一部受領</t>
         </is>
@@ -4917,7 +4917,7 @@
           <t>村提供実績データ 01／骨子案修正版 第4章(3)(6)</t>
         </is>
       </c>
-      <c r="E29" s="33" t="inlineStr">
+      <c r="E29" s="34" t="inlineStr">
         <is>
           <t>一部受領</t>
         </is>
@@ -4950,7 +4950,7 @@
           <t>村提供実績データ 01／骨子案修正版 第4章(4)</t>
         </is>
       </c>
-      <c r="E30" s="36" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
@@ -4983,7 +4983,7 @@
           <t>サービス見込量 12_別表第五判定／骨子案修正版 第1章6・第5章1／北塩原村_実態調査PDCAマニュアル_確認結果</t>
         </is>
       </c>
-      <c r="E31" s="36" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
@@ -4996,67 +4996,67 @@
       <c r="G31" s="37" t="n"/>
     </row>
     <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>要介護認定の有無・要介護度（匿名利用者一覧への列追加）</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>依頼済みの「年齢別・サービス別の匿名利用者一覧」に、要介護認定の有無・要介護度・利用している介護保険サービスの列を追加。確定版の調査票に介護保険の設問がないため、これが唯一の把握手段になる</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>クロス集計設計 A-1／サービス見込量 06_65歳移行判定</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G32" s="37" t="n"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>PDCAの評価体制・スケジュール・公表方法</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>自立支援協議会と庁内会議体の役割分担、実績把握と評価の時期（村の予算編成に合わせる）、中間評価の結果の公表方法（ホームページ・広報誌・協議会資料の公開範囲）</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>骨子案修正版 第1章6</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
+      <c r="E33" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F33" s="26" t="inlineStr">
         <is>
           <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="G32" s="37" t="n"/>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>アンケート調査票への村の修正指示</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>【受領済み】障がい者版17頁・障がい児版19頁のスキャンPDF。朱書き40か所。設問の削除・追加・順序変更のほか、削除理由として村の実データ9件が書き添えられている</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>村提供実績データ 05／北塩原村_アンケート調査票_村修正指示_確認結果</t>
-        </is>
-      </c>
-      <c r="E33" s="36" t="inlineStr">
-        <is>
-          <t>受領済</t>
-        </is>
-      </c>
-      <c r="F33" s="26" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G33" s="37" t="n"/>
@@ -5064,32 +5064,32 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="30" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
+          <t>アンケート調査票への村の修正指示</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>関連計画との整合確認</t>
+          <t>【受領済み】障がい者版17頁・障がい児版19頁のスキャンPDF。朱書き40か所。設問の削除・追加・順序変更のほか、削除理由として村の実データ9件が書き添えられている</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>計画本文 第1章・第7章</t>
-        </is>
-      </c>
-      <c r="E34" s="27" t="inlineStr">
-        <is>
-          <t>未受領</t>
+          <t>村提供実績データ 05／北塩原村_アンケート調査票_村修正指示_確認結果</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G34" s="37" t="n"/>
@@ -5102,17 +5102,17 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>40歳以上65歳未満の特定疾病該当者</t>
+          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+          <t>関連計画との整合確認</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量 02</t>
+          <t>計画本文 第1章・第7章</t>
         </is>
       </c>
       <c r="E35" s="27" t="inlineStr">
@@ -5135,43 +5135,76 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
+          <t>40歳以上65歳未満の特定疾病該当者</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>16の特定疾病に該当し要介護認定を受けている方の有無</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>サービス見込量 02</t>
+        </is>
+      </c>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G36" s="37" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
           <t>自立支援協議会の委員名簿</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>任期・氏名・所属・役職</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>計画書 資料編</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F37" s="26" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="G36" s="37" t="n"/>
-    </row>
-    <row r="38" ht="46" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>未受領：21件（うち最優先5件、高11件）、一部受領：3件。未受領の最優先案件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。「一部受領」は令和8年8月の調査票朱書きで数値の一部が判明したもので、基準日や内訳の確認が残っています（村提供実績データ 06 参照）。</t>
+      <c r="G37" s="37" t="n"/>
+    </row>
+    <row r="39" ht="46" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>未受領：22件（うち最優先6件、高11件）、一部受領：3件。未受領の最優先案件が揃わないとサービス見込量の個別積上げと手帳所持者数の年齢階級別推計を確定できません。8月5日期限の3件（対象者数、宛名ラベル、印刷仕様）はアンケート発送のクリティカルパス上にあります。「一部受領」は令和8年8月の調査票朱書きで数値の一部が判明したもので、基準日や内訳の確認が残っています（村提供実績データ 06 参照）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G36"/>
+  <autoFilter ref="A5:G37"/>
   <mergeCells count="3">
-    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5184,7 +5217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5443,7 +5476,7 @@
           <t>個人情報</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5628,7 +5661,7 @@
           <t>記述</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5665,7 +5698,7 @@
           <t>財源</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5702,7 +5735,7 @@
           <t>品質</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5756,12 +5789,12 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳と介護保険の認定情報の突合に一本化する</t>
+          <t>調査票が令和8年8月25日版で確定したため設問の追加は不可。支給決定者台帳と介護保険の要介護認定情報の突合に一本化する（クロス集計設計 A-1）。依頼済みの匿名利用者一覧に要介護認定の列を1つ追加する。アンケート側は問2×問27-1（C-12）、問2×問7（C-13）、問2×問27-3（C-14）で補う</t>
         </is>
       </c>
       <c r="G19" s="32" t="inlineStr">
         <is>
-          <t>判断待ち</t>
+          <t>対応中</t>
         </is>
       </c>
     </row>
@@ -5793,12 +5826,12 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>発送前であれば問13の後に外出目的の設問を追加するか、問45の選択肢を前回に揃える。発送後であれば別の把握方法へ切り替える旨を村と協議する</t>
+          <t>調査票が確定したため設問の追加は不可。確定版で最も近い問42は「今後参加したいもの」という意向であり、実態を問う前回値28.1%と接続できない。第4次障がい者計画は改定対象外のため、指標の測定方法の変更は村の判断事項。村との再協議が必要（クロス集計設計 S-1）</t>
         </is>
       </c>
       <c r="G20" s="30" t="inlineStr">
         <is>
-          <t>判断待ち</t>
+          <t>要対応</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5846,7 @@
           <t>供給</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5850,7 +5883,7 @@
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5887,7 +5920,7 @@
           <t>整合</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5924,7 +5957,7 @@
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5941,12 +5974,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>発送前であれば設問を追加する。追加しない場合は、村の朱書きで判明した区分6の2人について行動関連項目の点数を確認する（既に照会中）</t>
+          <t>調査票が確定したため設問の追加は不可。問19で「特にない」以外を選んだ回答をニーズ層として扱い（C-15・C-16）、実数は行政データ（区分6の2人の行動関連項目、行動援護の支給決定者数）で押さえる（クロス集計設計 A-2）。アンケートでは母数を特定できない旨を計画に明記する</t>
         </is>
       </c>
       <c r="G24" s="30" t="inlineStr">
         <is>
-          <t>判断待ち</t>
+          <t>対応中</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5994,7 @@
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5978,54 +6011,91 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>国の標準項目である旨を村へ伝えたうえで最終判断をいただく。当方の見解は変わらず、削除でも支障はない（区分別人数は役場データで把握済み）</t>
+          <t>令和8年8月25日版で削除が確定した。区分別人数15人は村から受領済みで、見込量の推計に支障はない。アンケート側は「重度層（代理指標）」で層別する（クロス集計設計 03・C-17）。区分別クロス集計ができないことは計画に明記する</t>
         </is>
       </c>
       <c r="G25" s="32" t="inlineStr">
         <is>
-          <t>判断待ち</t>
+          <t>完了</t>
         </is>
       </c>
     </row>
     <row r="26" ht="46" customHeight="1">
       <c r="A26" s="30" t="inlineStr">
         <is>
+          <t>R-22</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>国のマニュアルの発出と調査票の確定の時期が重なった</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>マニュアルは令和8年8月19日事務連絡（県通知8月24日）、調査票の確定は8月25日版。標準項目3件の欠落は、当方の設計の不備ではなくこの時期の重なりによる。第9期の策定時に同じ論点が生じうる</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>経緯を打合せ記録に残し、計画書の調査概要にも「調査票確定後に国のマニュアルが改定された」旨を注記する（クロス集計設計 S-4）。算定根拠への疑義に対する説明にもなる</t>
+        </is>
+      </c>
+      <c r="G26" s="30" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
           <t>R-19</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C26" s="30" t="inlineStr">
+      <c r="C27" s="32" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>障がい児版の設問番号に誤りがある</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>問11の選択肢番号「13」が2つある（「自傷、他害、強いこだわり、パニックなどへの対応」と「特にない」）。問10の選択肢番号は「3」が欠番。いずれも村の朱書きとは別に、通読して気づいたもの</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>調査票担当へ申し送り済み。印刷前に番号を振り直す。問10は問8との統合指示があるため、統合時に整理する</t>
         </is>
       </c>
-      <c r="G26" s="30" t="inlineStr">
+      <c r="G27" s="32" t="inlineStr">
         <is>
           <t>対応中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G26"/>
+  <autoFilter ref="A5:G27"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
